--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc2057430e44be2f/Documents/Year 5/Snake-Pit-Solver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_57E82D4BC9025C2602674A2340A3CD9A68A47DFB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA04825B-BA6E-41F9-A550-9BE481FFD75F}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_76F00E5D787F0755CC8E96C486143B179C088F86" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88E6AA81-F7E4-4B3F-B436-43DAE9BF1CCE}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="4635" windowWidth="23490" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lazy" sheetId="1" r:id="rId1"/>
@@ -435,13 +435,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:ALN7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="22.86328125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
     <col min="10" max="10" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="2" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" t="s">
         <v>2</v>
@@ -6455,7 +6455,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="3" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="5" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="6" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6">
         <v>1.42</v>
@@ -12478,7 +12478,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="7" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -12499,9 +12499,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:ALN11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15509,7 +15509,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="2" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" t="s">
         <v>2</v>
@@ -18515,7 +18515,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="3" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -18524,7 +18524,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="5" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -21532,3022 +21532,3022 @@
         <v>999</v>
       </c>
     </row>
-    <row r="6" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>33.14</v>
+        <v>21.95</v>
       </c>
       <c r="D6">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="E6">
+        <v>18.12</v>
+      </c>
+      <c r="F6">
+        <v>19.72</v>
+      </c>
+      <c r="G6">
+        <v>7.91</v>
+      </c>
+      <c r="H6">
+        <v>19.54</v>
+      </c>
+      <c r="I6">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="J6">
+        <v>26.89</v>
+      </c>
+      <c r="K6">
+        <v>16.41</v>
+      </c>
+      <c r="L6">
+        <v>21.65</v>
+      </c>
+      <c r="M6">
+        <v>21.11</v>
+      </c>
+      <c r="N6">
+        <v>20.86</v>
+      </c>
+      <c r="O6">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="P6">
+        <v>18.12</v>
+      </c>
+      <c r="Q6">
+        <v>10.64</v>
+      </c>
+      <c r="R6">
+        <v>13.77</v>
+      </c>
+      <c r="S6">
+        <v>19.920000000000002</v>
+      </c>
+      <c r="T6">
+        <v>12.29</v>
+      </c>
+      <c r="U6">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="V6">
+        <v>17.02</v>
+      </c>
+      <c r="W6">
+        <v>16.72</v>
+      </c>
+      <c r="X6">
+        <v>21.65</v>
+      </c>
+      <c r="Y6">
+        <v>10.3</v>
+      </c>
+      <c r="Z6">
+        <v>12.03</v>
+      </c>
+      <c r="AA6">
+        <v>15.2</v>
+      </c>
+      <c r="AB6">
+        <v>32.53</v>
+      </c>
+      <c r="AC6">
+        <v>9.35</v>
+      </c>
+      <c r="AD6">
+        <v>13.92</v>
+      </c>
+      <c r="AE6">
+        <v>26.45</v>
+      </c>
+      <c r="AF6">
+        <v>18.84</v>
+      </c>
+      <c r="AG6">
+        <v>14.25</v>
+      </c>
+      <c r="AH6">
+        <v>20.93</v>
+      </c>
+      <c r="AI6">
+        <v>7.58</v>
+      </c>
+      <c r="AJ6">
+        <v>15.45</v>
+      </c>
+      <c r="AK6">
+        <v>17.8</v>
+      </c>
+      <c r="AL6">
+        <v>17.64</v>
+      </c>
+      <c r="AM6">
+        <v>10.73</v>
+      </c>
+      <c r="AN6">
+        <v>23.12</v>
+      </c>
+      <c r="AO6">
+        <v>15.97</v>
+      </c>
+      <c r="AP6">
+        <v>17.079999999999998</v>
+      </c>
+      <c r="AQ6">
+        <v>15.79</v>
+      </c>
+      <c r="AR6">
+        <v>15.47</v>
+      </c>
+      <c r="AS6">
+        <v>9.14</v>
+      </c>
+      <c r="AT6">
+        <v>18.84</v>
+      </c>
+      <c r="AU6">
+        <v>14.93</v>
+      </c>
+      <c r="AV6">
+        <v>7.52</v>
+      </c>
+      <c r="AW6">
+        <v>14.33</v>
+      </c>
+      <c r="AX6">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="AY6">
+        <v>7.54</v>
+      </c>
+      <c r="AZ6">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="BA6">
+        <v>15.15</v>
+      </c>
+      <c r="BB6">
+        <v>23.21</v>
+      </c>
+      <c r="BC6">
+        <v>14.77</v>
+      </c>
+      <c r="BD6">
+        <v>9.23</v>
+      </c>
+      <c r="BE6">
+        <v>20.71</v>
+      </c>
+      <c r="BF6">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="BG6">
+        <v>15.79</v>
+      </c>
+      <c r="BH6">
+        <v>5.16</v>
+      </c>
+      <c r="BI6">
+        <v>10.18</v>
+      </c>
+      <c r="BJ6">
+        <v>17.18</v>
+      </c>
+      <c r="BK6">
+        <v>15.85</v>
+      </c>
+      <c r="BL6">
+        <v>17.82</v>
+      </c>
+      <c r="BM6">
+        <v>18.809999999999999</v>
+      </c>
+      <c r="BN6">
+        <v>15.74</v>
+      </c>
+      <c r="BO6">
+        <v>16.87</v>
+      </c>
+      <c r="BP6">
+        <v>22.95</v>
+      </c>
+      <c r="BQ6">
+        <v>11.95</v>
+      </c>
+      <c r="BR6">
+        <v>14.92</v>
+      </c>
+      <c r="BS6">
+        <v>17.14</v>
+      </c>
+      <c r="BT6">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="BU6">
+        <v>12.96</v>
+      </c>
+      <c r="BV6">
+        <v>25.56</v>
+      </c>
+      <c r="BW6">
+        <v>11.54</v>
+      </c>
+      <c r="BX6">
+        <v>15.03</v>
+      </c>
+      <c r="BY6">
+        <v>17.78</v>
+      </c>
+      <c r="BZ6">
+        <v>10.36</v>
+      </c>
+      <c r="CA6">
+        <v>12.16</v>
+      </c>
+      <c r="CB6">
+        <v>19.559999999999999</v>
+      </c>
+      <c r="CC6">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="CD6">
+        <v>15.77</v>
+      </c>
+      <c r="CE6">
+        <v>22.77</v>
+      </c>
+      <c r="CF6">
+        <v>16.47</v>
+      </c>
+      <c r="CG6">
+        <v>7.45</v>
+      </c>
+      <c r="CH6">
+        <v>19.32</v>
+      </c>
+      <c r="CI6">
+        <v>20.5</v>
+      </c>
+      <c r="CJ6">
+        <v>10.69</v>
+      </c>
+      <c r="CK6">
+        <v>10.61</v>
+      </c>
+      <c r="CL6">
+        <v>6.88</v>
+      </c>
+      <c r="CM6">
+        <v>11.03</v>
+      </c>
+      <c r="CN6">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="CO6">
+        <v>16.71</v>
+      </c>
+      <c r="CP6">
+        <v>14.39</v>
+      </c>
+      <c r="CQ6">
+        <v>13.18</v>
+      </c>
+      <c r="CR6">
+        <v>18.95</v>
+      </c>
+      <c r="CS6">
+        <v>18.440000000000001</v>
+      </c>
+      <c r="CT6">
+        <v>12.18</v>
+      </c>
+      <c r="CU6">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="CV6">
+        <v>21.21</v>
+      </c>
+      <c r="CW6">
+        <v>30.73</v>
+      </c>
+      <c r="CX6">
+        <v>16.11</v>
+      </c>
+      <c r="CY6">
+        <v>13.16</v>
+      </c>
+      <c r="CZ6">
+        <v>20.309999999999999</v>
+      </c>
+      <c r="DA6">
+        <v>12.58</v>
+      </c>
+      <c r="DB6">
+        <v>15.28</v>
+      </c>
+      <c r="DC6">
+        <v>19.579999999999998</v>
+      </c>
+      <c r="DD6">
+        <v>13.36</v>
+      </c>
+      <c r="DE6">
+        <v>9.26</v>
+      </c>
+      <c r="DF6">
+        <v>17.64</v>
+      </c>
+      <c r="DG6">
+        <v>10.01</v>
+      </c>
+      <c r="DH6">
+        <v>18.920000000000002</v>
+      </c>
+      <c r="DI6">
+        <v>19.61</v>
+      </c>
+      <c r="DJ6">
+        <v>16.72</v>
+      </c>
+      <c r="DK6">
+        <v>17.3</v>
+      </c>
+      <c r="DL6">
+        <v>11.3</v>
+      </c>
+      <c r="DM6">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="DN6">
+        <v>19.649999999999999</v>
+      </c>
+      <c r="DO6">
+        <v>18.16</v>
+      </c>
+      <c r="DP6">
+        <v>18.05</v>
+      </c>
+      <c r="DQ6">
+        <v>16.420000000000002</v>
+      </c>
+      <c r="DR6">
+        <v>15.24</v>
+      </c>
+      <c r="DS6">
+        <v>15.21</v>
+      </c>
+      <c r="DT6">
+        <v>12.85</v>
+      </c>
+      <c r="DU6">
+        <v>12.25</v>
+      </c>
+      <c r="DV6">
+        <v>20.350000000000001</v>
+      </c>
+      <c r="DW6">
+        <v>12.51</v>
+      </c>
+      <c r="DX6">
+        <v>22.13</v>
+      </c>
+      <c r="DY6">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="DZ6">
+        <v>18.96</v>
+      </c>
+      <c r="EA6">
+        <v>14.2</v>
+      </c>
+      <c r="EB6">
+        <v>16.45</v>
+      </c>
+      <c r="EC6">
+        <v>22.6</v>
+      </c>
+      <c r="ED6">
+        <v>15.84</v>
+      </c>
+      <c r="EE6">
+        <v>34.96</v>
+      </c>
+      <c r="EF6">
+        <v>12.51</v>
+      </c>
+      <c r="EG6">
+        <v>14.79</v>
+      </c>
+      <c r="EH6">
+        <v>21.15</v>
+      </c>
+      <c r="EI6">
+        <v>12.17</v>
+      </c>
+      <c r="EJ6">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="EK6">
+        <v>19.11</v>
+      </c>
+      <c r="EL6">
+        <v>14.38</v>
+      </c>
+      <c r="EM6">
+        <v>17.190000000000001</v>
+      </c>
+      <c r="EN6">
+        <v>13.15</v>
+      </c>
+      <c r="EO6">
+        <v>13.48</v>
+      </c>
+      <c r="EP6">
+        <v>28.2</v>
+      </c>
+      <c r="EQ6">
+        <v>5.01</v>
+      </c>
+      <c r="ER6">
+        <v>15.32</v>
+      </c>
+      <c r="ES6">
+        <v>13.67</v>
+      </c>
+      <c r="ET6">
+        <v>14.62</v>
+      </c>
+      <c r="EU6">
+        <v>6.63</v>
+      </c>
+      <c r="EV6">
+        <v>16.78</v>
+      </c>
+      <c r="EW6">
+        <v>15.71</v>
+      </c>
+      <c r="EX6">
+        <v>12.45</v>
+      </c>
+      <c r="EY6">
+        <v>13.16</v>
+      </c>
+      <c r="EZ6">
+        <v>19.809999999999999</v>
+      </c>
+      <c r="FA6">
+        <v>16.88</v>
+      </c>
+      <c r="FB6">
+        <v>17.78</v>
+      </c>
+      <c r="FC6">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="FD6">
+        <v>14.98</v>
+      </c>
+      <c r="FE6">
+        <v>13.75</v>
+      </c>
+      <c r="FF6">
+        <v>12.76</v>
+      </c>
+      <c r="FG6">
+        <v>16.14</v>
+      </c>
+      <c r="FH6">
+        <v>20.96</v>
+      </c>
+      <c r="FI6">
+        <v>16.39</v>
+      </c>
+      <c r="FJ6">
+        <v>14.18</v>
+      </c>
+      <c r="FK6">
+        <v>13.63</v>
+      </c>
+      <c r="FL6">
+        <v>11.82</v>
+      </c>
+      <c r="FM6">
+        <v>19.55</v>
+      </c>
+      <c r="FN6">
+        <v>12.57</v>
+      </c>
+      <c r="FO6">
+        <v>17.87</v>
+      </c>
+      <c r="FP6">
+        <v>12.22</v>
+      </c>
+      <c r="FQ6">
+        <v>15.03</v>
+      </c>
+      <c r="FR6">
+        <v>13.46</v>
+      </c>
+      <c r="FS6">
+        <v>20.91</v>
+      </c>
+      <c r="FT6">
+        <v>21.14</v>
+      </c>
+      <c r="FU6">
+        <v>15.15</v>
+      </c>
+      <c r="FV6">
+        <v>9.35</v>
+      </c>
+      <c r="FW6">
+        <v>13.62</v>
+      </c>
+      <c r="FX6">
+        <v>13.22</v>
+      </c>
+      <c r="FY6">
+        <v>14.85</v>
+      </c>
+      <c r="FZ6">
+        <v>14.88</v>
+      </c>
+      <c r="GA6">
+        <v>10.74</v>
+      </c>
+      <c r="GB6">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="GC6">
+        <v>12.74</v>
+      </c>
+      <c r="GD6">
+        <v>14.61</v>
+      </c>
+      <c r="GE6">
+        <v>11.97</v>
+      </c>
+      <c r="GF6">
+        <v>19.29</v>
+      </c>
+      <c r="GG6">
+        <v>12.39</v>
+      </c>
+      <c r="GH6">
+        <v>9.59</v>
+      </c>
+      <c r="GI6">
+        <v>14.73</v>
+      </c>
+      <c r="GJ6">
+        <v>47.38</v>
+      </c>
+      <c r="GK6">
+        <v>11.33</v>
+      </c>
+      <c r="GL6">
+        <v>17.420000000000002</v>
+      </c>
+      <c r="GM6">
+        <v>16</v>
+      </c>
+      <c r="GN6">
+        <v>14.63</v>
+      </c>
+      <c r="GO6">
+        <v>22.23</v>
+      </c>
+      <c r="GP6">
+        <v>17.3</v>
+      </c>
+      <c r="GQ6">
+        <v>18.32</v>
+      </c>
+      <c r="GR6">
+        <v>18.57</v>
+      </c>
+      <c r="GS6">
+        <v>20.54</v>
+      </c>
+      <c r="GT6">
+        <v>20.52</v>
+      </c>
+      <c r="GU6">
+        <v>12.43</v>
+      </c>
+      <c r="GV6">
+        <v>10.57</v>
+      </c>
+      <c r="GW6">
+        <v>12.61</v>
+      </c>
+      <c r="GX6">
+        <v>7.83</v>
+      </c>
+      <c r="GY6">
+        <v>19.420000000000002</v>
+      </c>
+      <c r="GZ6">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="HA6">
+        <v>19.09</v>
+      </c>
+      <c r="HB6">
+        <v>12.95</v>
+      </c>
+      <c r="HC6">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="HD6">
+        <v>17.66</v>
+      </c>
+      <c r="HE6">
+        <v>13.53</v>
+      </c>
+      <c r="HF6">
+        <v>18.48</v>
+      </c>
+      <c r="HG6">
+        <v>9.34</v>
+      </c>
+      <c r="HH6">
+        <v>10.93</v>
+      </c>
+      <c r="HI6">
+        <v>14.54</v>
+      </c>
+      <c r="HJ6">
+        <v>17.29</v>
+      </c>
+      <c r="HK6">
+        <v>21.2</v>
+      </c>
+      <c r="HL6">
+        <v>10.32</v>
+      </c>
+      <c r="HM6">
+        <v>13.46</v>
+      </c>
+      <c r="HN6">
+        <v>23.89</v>
+      </c>
+      <c r="HO6">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="HP6">
+        <v>17.010000000000002</v>
+      </c>
+      <c r="HQ6">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="HR6">
+        <v>23.32</v>
+      </c>
+      <c r="HS6">
+        <v>12.76</v>
+      </c>
+      <c r="HT6">
+        <v>9.26</v>
+      </c>
+      <c r="HU6">
+        <v>17.96</v>
+      </c>
+      <c r="HV6">
+        <v>7.54</v>
+      </c>
+      <c r="HW6">
+        <v>14.01</v>
+      </c>
+      <c r="HX6">
+        <v>16.54</v>
+      </c>
+      <c r="HY6">
+        <v>11.57</v>
+      </c>
+      <c r="HZ6">
+        <v>14.02</v>
+      </c>
+      <c r="IA6">
+        <v>12.09</v>
+      </c>
+      <c r="IB6">
+        <v>9.57</v>
+      </c>
+      <c r="IC6">
+        <v>9.18</v>
+      </c>
+      <c r="ID6">
+        <v>16.75</v>
+      </c>
+      <c r="IE6">
+        <v>15.83</v>
+      </c>
+      <c r="IF6">
+        <v>17.03</v>
+      </c>
+      <c r="IG6">
+        <v>11.59</v>
+      </c>
+      <c r="IH6">
+        <v>12.9</v>
+      </c>
+      <c r="II6">
+        <v>20.02</v>
+      </c>
+      <c r="IJ6">
+        <v>14.7</v>
+      </c>
+      <c r="IK6">
+        <v>12.28</v>
+      </c>
+      <c r="IL6">
+        <v>21.58</v>
+      </c>
+      <c r="IM6">
+        <v>17.77</v>
+      </c>
+      <c r="IN6">
+        <v>21.62</v>
+      </c>
+      <c r="IO6">
+        <v>15.28</v>
+      </c>
+      <c r="IP6">
+        <v>15.17</v>
+      </c>
+      <c r="IQ6">
+        <v>12.25</v>
+      </c>
+      <c r="IR6">
+        <v>18.14</v>
+      </c>
+      <c r="IS6">
+        <v>12.06</v>
+      </c>
+      <c r="IT6">
+        <v>9.9700000000000006</v>
+      </c>
+      <c r="IU6">
+        <v>16.12</v>
+      </c>
+      <c r="IV6">
+        <v>15.11</v>
+      </c>
+      <c r="IW6">
+        <v>7.64</v>
+      </c>
+      <c r="IX6">
+        <v>21.4</v>
+      </c>
+      <c r="IY6">
+        <v>14.78</v>
+      </c>
+      <c r="IZ6">
+        <v>19.55</v>
+      </c>
+      <c r="JA6">
+        <v>15.55</v>
+      </c>
+      <c r="JB6">
+        <v>14.94</v>
+      </c>
+      <c r="JC6">
+        <v>13.65</v>
+      </c>
+      <c r="JD6">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="JE6">
+        <v>14.3</v>
+      </c>
+      <c r="JF6">
+        <v>19.55</v>
+      </c>
+      <c r="JG6">
+        <v>18.03</v>
+      </c>
+      <c r="JH6">
+        <v>14.01</v>
+      </c>
+      <c r="JI6">
+        <v>10.46</v>
+      </c>
+      <c r="JJ6">
+        <v>20.21</v>
+      </c>
+      <c r="JK6">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="JL6">
+        <v>35.85</v>
+      </c>
+      <c r="JM6">
+        <v>22.42</v>
+      </c>
+      <c r="JN6">
+        <v>13.61</v>
+      </c>
+      <c r="JO6">
+        <v>14.86</v>
+      </c>
+      <c r="JP6">
+        <v>19.559999999999999</v>
+      </c>
+      <c r="JQ6">
+        <v>17.48</v>
+      </c>
+      <c r="JR6">
+        <v>13.01</v>
+      </c>
+      <c r="JS6">
+        <v>13.16</v>
+      </c>
+      <c r="JT6">
+        <v>15.96</v>
+      </c>
+      <c r="JU6">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="JV6">
+        <v>23.65</v>
+      </c>
+      <c r="JW6">
+        <v>13.8</v>
+      </c>
+      <c r="JX6">
+        <v>14.29</v>
+      </c>
+      <c r="JY6">
+        <v>22.4</v>
+      </c>
+      <c r="JZ6">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="KA6">
+        <v>6.93</v>
+      </c>
+      <c r="KB6">
+        <v>19.59</v>
+      </c>
+      <c r="KC6">
+        <v>21.13</v>
+      </c>
+      <c r="KD6">
+        <v>14.89</v>
+      </c>
+      <c r="KE6">
+        <v>21.04</v>
+      </c>
+      <c r="KF6">
+        <v>15.84</v>
+      </c>
+      <c r="KG6">
+        <v>9.42</v>
+      </c>
+      <c r="KH6">
+        <v>8.4</v>
+      </c>
+      <c r="KI6">
+        <v>12.64</v>
+      </c>
+      <c r="KJ6">
+        <v>22.48</v>
+      </c>
+      <c r="KK6">
+        <v>15.44</v>
+      </c>
+      <c r="KL6">
+        <v>11.63</v>
+      </c>
+      <c r="KM6">
+        <v>18.57</v>
+      </c>
+      <c r="KN6">
+        <v>15.75</v>
+      </c>
+      <c r="KO6">
+        <v>17.760000000000002</v>
+      </c>
+      <c r="KP6">
+        <v>14.85</v>
+      </c>
+      <c r="KQ6">
+        <v>15.32</v>
+      </c>
+      <c r="KR6">
+        <v>13.71</v>
+      </c>
+      <c r="KS6">
+        <v>17.36</v>
+      </c>
+      <c r="KT6">
+        <v>13.82</v>
+      </c>
+      <c r="KU6">
+        <v>12.94</v>
+      </c>
+      <c r="KV6">
+        <v>12.07</v>
+      </c>
+      <c r="KW6">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="KX6">
+        <v>22.5</v>
+      </c>
+      <c r="KY6">
+        <v>11.12</v>
+      </c>
+      <c r="KZ6">
+        <v>13.71</v>
+      </c>
+      <c r="LA6">
+        <v>16.73</v>
+      </c>
+      <c r="LB6">
+        <v>15.45</v>
+      </c>
+      <c r="LC6">
+        <v>16.37</v>
+      </c>
+      <c r="LD6">
+        <v>16.64</v>
+      </c>
+      <c r="LE6">
+        <v>17.03</v>
+      </c>
+      <c r="LF6">
+        <v>16.23</v>
+      </c>
+      <c r="LG6">
+        <v>14.82</v>
+      </c>
+      <c r="LH6">
+        <v>16.649999999999999</v>
+      </c>
+      <c r="LI6">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="LJ6">
+        <v>16.8</v>
+      </c>
+      <c r="LK6">
+        <v>12.37</v>
+      </c>
+      <c r="LL6">
+        <v>22.09</v>
+      </c>
+      <c r="LM6">
+        <v>15.92</v>
+      </c>
+      <c r="LN6">
+        <v>19.3</v>
+      </c>
+      <c r="LO6">
+        <v>16.55</v>
+      </c>
+      <c r="LP6">
+        <v>19.8</v>
+      </c>
+      <c r="LQ6">
+        <v>13.72</v>
+      </c>
+      <c r="LR6">
+        <v>23.84</v>
+      </c>
+      <c r="LS6">
+        <v>26.03</v>
+      </c>
+      <c r="LT6">
+        <v>15.55</v>
+      </c>
+      <c r="LU6">
+        <v>19.22</v>
+      </c>
+      <c r="LV6">
+        <v>18.920000000000002</v>
+      </c>
+      <c r="LW6">
+        <v>14.21</v>
+      </c>
+      <c r="LX6">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="LY6">
+        <v>15.25</v>
+      </c>
+      <c r="LZ6">
+        <v>22.51</v>
+      </c>
+      <c r="MA6">
+        <v>14.24</v>
+      </c>
+      <c r="MB6">
+        <v>19.79</v>
+      </c>
+      <c r="MC6">
+        <v>8.19</v>
+      </c>
+      <c r="MD6">
+        <v>18.7</v>
+      </c>
+      <c r="ME6">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="MF6">
+        <v>22.06</v>
+      </c>
+      <c r="MG6">
+        <v>11.82</v>
+      </c>
+      <c r="MH6">
+        <v>16.18</v>
+      </c>
+      <c r="MI6">
+        <v>20.05</v>
+      </c>
+      <c r="MJ6">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="MK6">
+        <v>22.44</v>
+      </c>
+      <c r="ML6">
+        <v>19.850000000000001</v>
+      </c>
+      <c r="MM6">
+        <v>20.25</v>
+      </c>
+      <c r="MN6">
+        <v>27.98</v>
+      </c>
+      <c r="MO6">
+        <v>19.489999999999998</v>
+      </c>
+      <c r="MP6">
+        <v>18.97</v>
+      </c>
+      <c r="MQ6">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="MR6">
+        <v>14.71</v>
+      </c>
+      <c r="MS6">
+        <v>17.91</v>
+      </c>
+      <c r="MT6">
+        <v>11</v>
+      </c>
+      <c r="MU6">
+        <v>21.39</v>
+      </c>
+      <c r="MV6">
+        <v>20.86</v>
+      </c>
+      <c r="MW6">
+        <v>16.27</v>
+      </c>
+      <c r="MX6">
+        <v>24.38</v>
+      </c>
+      <c r="MY6">
+        <v>18.05</v>
+      </c>
+      <c r="MZ6">
+        <v>24.72</v>
+      </c>
+      <c r="NA6">
+        <v>18.14</v>
+      </c>
+      <c r="NB6">
+        <v>14.12</v>
+      </c>
+      <c r="NC6">
+        <v>17.72</v>
+      </c>
+      <c r="ND6">
+        <v>32.1</v>
+      </c>
+      <c r="NE6">
+        <v>15.05</v>
+      </c>
+      <c r="NF6">
+        <v>19.77</v>
+      </c>
+      <c r="NG6">
+        <v>8.84</v>
+      </c>
+      <c r="NH6">
+        <v>17.63</v>
+      </c>
+      <c r="NI6">
+        <v>16.59</v>
+      </c>
+      <c r="NJ6">
+        <v>18.32</v>
+      </c>
+      <c r="NK6">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="NL6">
+        <v>33.130000000000003</v>
+      </c>
+      <c r="NM6">
+        <v>11.73</v>
+      </c>
+      <c r="NN6">
+        <v>18.010000000000002</v>
+      </c>
+      <c r="NO6">
+        <v>16.95</v>
+      </c>
+      <c r="NP6">
+        <v>11.96</v>
+      </c>
+      <c r="NQ6">
+        <v>18.18</v>
+      </c>
+      <c r="NR6">
+        <v>21.39</v>
+      </c>
+      <c r="NS6">
+        <v>14.63</v>
+      </c>
+      <c r="NT6">
+        <v>23.4</v>
+      </c>
+      <c r="NU6">
+        <v>15.46</v>
+      </c>
+      <c r="NV6">
+        <v>16.37</v>
+      </c>
+      <c r="NW6">
+        <v>14.51</v>
+      </c>
+      <c r="NX6">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="NY6">
+        <v>17.75</v>
+      </c>
+      <c r="NZ6">
+        <v>15.62</v>
+      </c>
+      <c r="OA6">
+        <v>19.53</v>
+      </c>
+      <c r="OB6">
+        <v>9.92</v>
+      </c>
+      <c r="OC6">
+        <v>17.989999999999998</v>
+      </c>
+      <c r="OD6">
+        <v>15.09</v>
+      </c>
+      <c r="OE6">
+        <v>14.83</v>
+      </c>
+      <c r="OF6">
+        <v>22.13</v>
+      </c>
+      <c r="OG6">
+        <v>13.28</v>
+      </c>
+      <c r="OH6">
+        <v>10.54</v>
+      </c>
+      <c r="OI6">
+        <v>17.829999999999998</v>
+      </c>
+      <c r="OJ6">
+        <v>13.39</v>
+      </c>
+      <c r="OK6">
+        <v>26.54</v>
+      </c>
+      <c r="OL6">
+        <v>13.13</v>
+      </c>
+      <c r="OM6">
+        <v>15.68</v>
+      </c>
+      <c r="ON6">
+        <v>20.420000000000002</v>
+      </c>
+      <c r="OO6">
+        <v>19.95</v>
+      </c>
+      <c r="OP6">
+        <v>20.96</v>
+      </c>
+      <c r="OQ6">
+        <v>13.2</v>
+      </c>
+      <c r="OR6">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="OS6">
+        <v>5.68</v>
+      </c>
+      <c r="OT6">
+        <v>9</v>
+      </c>
+      <c r="OU6">
+        <v>17.13</v>
+      </c>
+      <c r="OV6">
+        <v>17.62</v>
+      </c>
+      <c r="OW6">
+        <v>17.95</v>
+      </c>
+      <c r="OX6">
+        <v>15.38</v>
+      </c>
+      <c r="OY6">
+        <v>28.99</v>
+      </c>
+      <c r="OZ6">
+        <v>11.17</v>
+      </c>
+      <c r="PA6">
+        <v>9.48</v>
+      </c>
+      <c r="PB6">
+        <v>14.78</v>
+      </c>
+      <c r="PC6">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="PD6">
+        <v>28.82</v>
+      </c>
+      <c r="PE6">
+        <v>13</v>
+      </c>
+      <c r="PF6">
+        <v>15.56</v>
+      </c>
+      <c r="PG6">
+        <v>10.62</v>
+      </c>
+      <c r="PH6">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="PI6">
+        <v>16.2</v>
+      </c>
+      <c r="PJ6">
+        <v>13.7</v>
+      </c>
+      <c r="PK6">
+        <v>12.16</v>
+      </c>
+      <c r="PL6">
+        <v>16.14</v>
+      </c>
+      <c r="PM6">
+        <v>28.3</v>
+      </c>
+      <c r="PN6">
+        <v>15.73</v>
+      </c>
+      <c r="PO6">
+        <v>19.190000000000001</v>
+      </c>
+      <c r="PP6">
+        <v>9.85</v>
+      </c>
+      <c r="PQ6">
+        <v>12.46</v>
+      </c>
+      <c r="PR6">
+        <v>17.28</v>
+      </c>
+      <c r="PS6">
+        <v>11.22</v>
+      </c>
+      <c r="PT6">
+        <v>13.27</v>
+      </c>
+      <c r="PU6">
+        <v>21.31</v>
+      </c>
+      <c r="PV6">
+        <v>12.19</v>
+      </c>
+      <c r="PW6">
+        <v>12.16</v>
+      </c>
+      <c r="PX6">
+        <v>18.11</v>
+      </c>
+      <c r="PY6">
+        <v>20.75</v>
+      </c>
+      <c r="PZ6">
+        <v>15.33</v>
+      </c>
+      <c r="QA6">
+        <v>15.65</v>
+      </c>
+      <c r="QB6">
+        <v>10.130000000000001</v>
+      </c>
+      <c r="QC6">
+        <v>6.64</v>
+      </c>
+      <c r="QD6">
+        <v>15.11</v>
+      </c>
+      <c r="QE6">
+        <v>15.3</v>
+      </c>
+      <c r="QF6">
+        <v>14.27</v>
+      </c>
+      <c r="QG6">
+        <v>17.79</v>
+      </c>
+      <c r="QH6">
+        <v>14</v>
+      </c>
+      <c r="QI6">
+        <v>15.58</v>
+      </c>
+      <c r="QJ6">
+        <v>16.04</v>
+      </c>
+      <c r="QK6">
+        <v>9.17</v>
+      </c>
+      <c r="QL6">
+        <v>14.5</v>
+      </c>
+      <c r="QM6">
+        <v>15.28</v>
+      </c>
+      <c r="QN6">
+        <v>18.05</v>
+      </c>
+      <c r="QO6">
+        <v>20.85</v>
+      </c>
+      <c r="QP6">
+        <v>8.5</v>
+      </c>
+      <c r="QQ6">
         <v>13.96</v>
       </c>
-      <c r="E6">
-        <v>32.79</v>
-      </c>
-      <c r="F6">
-        <v>22.61</v>
-      </c>
-      <c r="G6">
-        <v>13.42</v>
-      </c>
-      <c r="H6">
-        <v>36.96</v>
-      </c>
-      <c r="I6">
-        <v>22.84</v>
-      </c>
-      <c r="J6">
-        <v>41.64</v>
-      </c>
-      <c r="K6">
-        <v>26.23</v>
-      </c>
-      <c r="L6">
-        <v>26.06</v>
-      </c>
-      <c r="M6">
-        <v>17.13</v>
-      </c>
-      <c r="N6">
-        <v>28.17</v>
-      </c>
-      <c r="O6">
-        <v>28.19</v>
-      </c>
-      <c r="P6">
-        <v>22.87</v>
-      </c>
-      <c r="Q6">
-        <v>30.94</v>
-      </c>
-      <c r="R6">
-        <v>29.73</v>
-      </c>
-      <c r="S6">
-        <v>25.06</v>
-      </c>
-      <c r="T6">
-        <v>4.58</v>
-      </c>
-      <c r="U6">
-        <v>33.99</v>
-      </c>
-      <c r="V6">
-        <v>25.51</v>
-      </c>
-      <c r="W6">
-        <v>9.6</v>
-      </c>
-      <c r="X6">
+      <c r="QR6">
+        <v>13.2</v>
+      </c>
+      <c r="QS6">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="QT6">
+        <v>15.63</v>
+      </c>
+      <c r="QU6">
+        <v>21.9</v>
+      </c>
+      <c r="QV6">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="QW6">
+        <v>10.6</v>
+      </c>
+      <c r="QX6">
+        <v>15.54</v>
+      </c>
+      <c r="QY6">
+        <v>15.16</v>
+      </c>
+      <c r="QZ6">
+        <v>13.52</v>
+      </c>
+      <c r="RA6">
+        <v>20.73</v>
+      </c>
+      <c r="RB6">
+        <v>19.440000000000001</v>
+      </c>
+      <c r="RC6">
+        <v>19.53</v>
+      </c>
+      <c r="RD6">
+        <v>16.87</v>
+      </c>
+      <c r="RE6">
+        <v>18.91</v>
+      </c>
+      <c r="RF6">
+        <v>19.09</v>
+      </c>
+      <c r="RG6">
+        <v>8.85</v>
+      </c>
+      <c r="RH6">
+        <v>18.55</v>
+      </c>
+      <c r="RI6">
+        <v>10.86</v>
+      </c>
+      <c r="RJ6">
+        <v>12.65</v>
+      </c>
+      <c r="RK6">
+        <v>11.41</v>
+      </c>
+      <c r="RL6">
+        <v>13.93</v>
+      </c>
+      <c r="RM6">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="RN6">
+        <v>17.23</v>
+      </c>
+      <c r="RO6">
+        <v>10.46</v>
+      </c>
+      <c r="RP6">
+        <v>15.37</v>
+      </c>
+      <c r="RQ6">
+        <v>13.07</v>
+      </c>
+      <c r="RR6">
+        <v>12.34</v>
+      </c>
+      <c r="RS6">
+        <v>11.81</v>
+      </c>
+      <c r="RT6">
+        <v>15.86</v>
+      </c>
+      <c r="RU6">
+        <v>19.03</v>
+      </c>
+      <c r="RV6">
+        <v>9.34</v>
+      </c>
+      <c r="RW6">
+        <v>23</v>
+      </c>
+      <c r="RX6">
+        <v>10.59</v>
+      </c>
+      <c r="RY6">
+        <v>11.13</v>
+      </c>
+      <c r="RZ6">
+        <v>17.04</v>
+      </c>
+      <c r="SA6">
+        <v>12.01</v>
+      </c>
+      <c r="SB6">
+        <v>12.31</v>
+      </c>
+      <c r="SC6">
+        <v>14.9</v>
+      </c>
+      <c r="SD6">
+        <v>15.15</v>
+      </c>
+      <c r="SE6">
+        <v>22.75</v>
+      </c>
+      <c r="SF6">
+        <v>26.53</v>
+      </c>
+      <c r="SG6">
+        <v>13.78</v>
+      </c>
+      <c r="SH6">
+        <v>15.86</v>
+      </c>
+      <c r="SI6">
+        <v>15.4</v>
+      </c>
+      <c r="SJ6">
+        <v>11.28</v>
+      </c>
+      <c r="SK6">
+        <v>11.95</v>
+      </c>
+      <c r="SL6">
+        <v>18.79</v>
+      </c>
+      <c r="SM6">
+        <v>26.78</v>
+      </c>
+      <c r="SN6">
+        <v>14.18</v>
+      </c>
+      <c r="SO6">
+        <v>17.78</v>
+      </c>
+      <c r="SP6">
+        <v>6.64</v>
+      </c>
+      <c r="SQ6">
+        <v>18.16</v>
+      </c>
+      <c r="SR6">
+        <v>14.56</v>
+      </c>
+      <c r="SS6">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="ST6">
+        <v>17.940000000000001</v>
+      </c>
+      <c r="SU6">
+        <v>18.16</v>
+      </c>
+      <c r="SV6">
+        <v>10.3</v>
+      </c>
+      <c r="SW6">
+        <v>15.15</v>
+      </c>
+      <c r="SX6">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="SY6">
+        <v>15.62</v>
+      </c>
+      <c r="SZ6">
+        <v>6.18</v>
+      </c>
+      <c r="TA6">
+        <v>11.43</v>
+      </c>
+      <c r="TB6">
+        <v>24.2</v>
+      </c>
+      <c r="TC6">
+        <v>14.44</v>
+      </c>
+      <c r="TD6">
+        <v>20.16</v>
+      </c>
+      <c r="TE6">
+        <v>17.95</v>
+      </c>
+      <c r="TF6">
+        <v>12.12</v>
+      </c>
+      <c r="TG6">
+        <v>13.18</v>
+      </c>
+      <c r="TH6">
+        <v>21.29</v>
+      </c>
+      <c r="TI6">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="TJ6">
+        <v>12.92</v>
+      </c>
+      <c r="TK6">
+        <v>16.920000000000002</v>
+      </c>
+      <c r="TL6">
+        <v>15.28</v>
+      </c>
+      <c r="TM6">
+        <v>13.23</v>
+      </c>
+      <c r="TN6">
+        <v>18.73</v>
+      </c>
+      <c r="TO6">
+        <v>11.32</v>
+      </c>
+      <c r="TP6">
+        <v>9.18</v>
+      </c>
+      <c r="TQ6">
+        <v>15.59</v>
+      </c>
+      <c r="TR6">
+        <v>17.55</v>
+      </c>
+      <c r="TS6">
         <v>18.75</v>
       </c>
-      <c r="Y6">
-        <v>29.44</v>
-      </c>
-      <c r="Z6">
-        <v>24.1</v>
-      </c>
-      <c r="AA6">
-        <v>31.03</v>
-      </c>
-      <c r="AB6">
-        <v>24.44</v>
-      </c>
-      <c r="AC6">
-        <v>27.04</v>
-      </c>
-      <c r="AD6">
-        <v>15.97</v>
-      </c>
-      <c r="AE6">
-        <v>24.8</v>
-      </c>
-      <c r="AF6">
-        <v>19.98</v>
-      </c>
-      <c r="AG6">
-        <v>33</v>
-      </c>
-      <c r="AH6">
-        <v>22.2</v>
-      </c>
-      <c r="AI6">
-        <v>35.5</v>
-      </c>
-      <c r="AJ6">
-        <v>24.41</v>
-      </c>
-      <c r="AK6">
-        <v>38.159999999999997</v>
-      </c>
-      <c r="AL6">
-        <v>28.04</v>
-      </c>
-      <c r="AM6">
-        <v>27.34</v>
-      </c>
-      <c r="AN6">
-        <v>23.23</v>
-      </c>
-      <c r="AO6">
-        <v>16.059999999999999</v>
-      </c>
-      <c r="AP6">
-        <v>14.8</v>
-      </c>
-      <c r="AQ6">
-        <v>26.07</v>
-      </c>
-      <c r="AR6">
-        <v>29.34</v>
-      </c>
-      <c r="AS6">
-        <v>17.190000000000001</v>
-      </c>
-      <c r="AT6">
-        <v>29.34</v>
-      </c>
-      <c r="AU6">
-        <v>21.19</v>
-      </c>
-      <c r="AV6">
-        <v>15.18</v>
-      </c>
-      <c r="AW6">
+      <c r="TT6">
+        <v>17.05</v>
+      </c>
+      <c r="TU6">
+        <v>18.03</v>
+      </c>
+      <c r="TV6">
+        <v>28.54</v>
+      </c>
+      <c r="TW6">
+        <v>15.37</v>
+      </c>
+      <c r="TX6">
+        <v>19.23</v>
+      </c>
+      <c r="TY6">
+        <v>14.36</v>
+      </c>
+      <c r="TZ6">
+        <v>10.54</v>
+      </c>
+      <c r="UA6">
+        <v>14.51</v>
+      </c>
+      <c r="UB6">
+        <v>16.96</v>
+      </c>
+      <c r="UC6">
+        <v>9.57</v>
+      </c>
+      <c r="UD6">
+        <v>20.13</v>
+      </c>
+      <c r="UE6">
+        <v>11.72</v>
+      </c>
+      <c r="UF6">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="UG6">
+        <v>27.13</v>
+      </c>
+      <c r="UH6">
+        <v>15.24</v>
+      </c>
+      <c r="UI6">
+        <v>16.489999999999998</v>
+      </c>
+      <c r="UJ6">
+        <v>19.809999999999999</v>
+      </c>
+      <c r="UK6">
+        <v>10.88</v>
+      </c>
+      <c r="UL6">
+        <v>9.1</v>
+      </c>
+      <c r="UM6">
+        <v>11.72</v>
+      </c>
+      <c r="UN6">
+        <v>11.78</v>
+      </c>
+      <c r="UO6">
+        <v>10.5</v>
+      </c>
+      <c r="UP6">
+        <v>14.87</v>
+      </c>
+      <c r="UQ6">
+        <v>9.16</v>
+      </c>
+      <c r="UR6">
+        <v>15.68</v>
+      </c>
+      <c r="US6">
+        <v>12.29</v>
+      </c>
+      <c r="UT6">
+        <v>6.67</v>
+      </c>
+      <c r="UU6">
+        <v>10.8</v>
+      </c>
+      <c r="UV6">
+        <v>6.54</v>
+      </c>
+      <c r="UW6">
+        <v>25.16</v>
+      </c>
+      <c r="UX6">
+        <v>13.65</v>
+      </c>
+      <c r="UY6">
+        <v>32.090000000000003</v>
+      </c>
+      <c r="UZ6">
+        <v>14.85</v>
+      </c>
+      <c r="VA6">
+        <v>11.17</v>
+      </c>
+      <c r="VB6">
+        <v>16.64</v>
+      </c>
+      <c r="VC6">
+        <v>13.72</v>
+      </c>
+      <c r="VD6">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="VE6">
+        <v>15.54</v>
+      </c>
+      <c r="VF6">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="VG6">
+        <v>26.28</v>
+      </c>
+      <c r="VH6">
+        <v>21.58</v>
+      </c>
+      <c r="VI6">
+        <v>18.77</v>
+      </c>
+      <c r="VJ6">
+        <v>8.86</v>
+      </c>
+      <c r="VK6">
+        <v>14.57</v>
+      </c>
+      <c r="VL6">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="VM6">
+        <v>7.79</v>
+      </c>
+      <c r="VN6">
+        <v>9.36</v>
+      </c>
+      <c r="VO6">
+        <v>16.809999999999999</v>
+      </c>
+      <c r="VP6">
+        <v>23.04</v>
+      </c>
+      <c r="VQ6">
+        <v>13.61</v>
+      </c>
+      <c r="VR6">
+        <v>15.34</v>
+      </c>
+      <c r="VS6">
+        <v>15.89</v>
+      </c>
+      <c r="VT6">
+        <v>11.01</v>
+      </c>
+      <c r="VU6">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="VV6">
+        <v>13.98</v>
+      </c>
+      <c r="VW6">
+        <v>18.39</v>
+      </c>
+      <c r="VX6">
+        <v>9.23</v>
+      </c>
+      <c r="VY6">
+        <v>14.27</v>
+      </c>
+      <c r="VZ6">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="WA6">
+        <v>18.510000000000002</v>
+      </c>
+      <c r="WB6">
+        <v>19.559999999999999</v>
+      </c>
+      <c r="WC6">
+        <v>18.43</v>
+      </c>
+      <c r="WD6">
+        <v>9.24</v>
+      </c>
+      <c r="WE6">
+        <v>11.58</v>
+      </c>
+      <c r="WF6">
+        <v>15.9</v>
+      </c>
+      <c r="WG6">
+        <v>15.64</v>
+      </c>
+      <c r="WH6">
+        <v>12.7</v>
+      </c>
+      <c r="WI6">
+        <v>13.29</v>
+      </c>
+      <c r="WJ6">
+        <v>13.09</v>
+      </c>
+      <c r="WK6">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="WL6">
+        <v>47.65</v>
+      </c>
+      <c r="WM6">
+        <v>7.1</v>
+      </c>
+      <c r="WN6">
+        <v>13.3</v>
+      </c>
+      <c r="WO6">
+        <v>23.06</v>
+      </c>
+      <c r="WP6">
+        <v>24.55</v>
+      </c>
+      <c r="WQ6">
+        <v>20.49</v>
+      </c>
+      <c r="WR6">
+        <v>11.69</v>
+      </c>
+      <c r="WS6">
+        <v>17.809999999999999</v>
+      </c>
+      <c r="WT6">
+        <v>16.21</v>
+      </c>
+      <c r="WU6">
+        <v>16.75</v>
+      </c>
+      <c r="WV6">
+        <v>17.079999999999998</v>
+      </c>
+      <c r="WW6">
+        <v>17.82</v>
+      </c>
+      <c r="WX6">
+        <v>19.02</v>
+      </c>
+      <c r="WY6">
+        <v>21.81</v>
+      </c>
+      <c r="WZ6">
+        <v>16.48</v>
+      </c>
+      <c r="XA6">
+        <v>10.98</v>
+      </c>
+      <c r="XB6">
+        <v>13.91</v>
+      </c>
+      <c r="XC6">
+        <v>17.18</v>
+      </c>
+      <c r="XD6">
+        <v>20.6</v>
+      </c>
+      <c r="XE6">
+        <v>11.95</v>
+      </c>
+      <c r="XF6">
+        <v>17.3</v>
+      </c>
+      <c r="XG6">
+        <v>19.420000000000002</v>
+      </c>
+      <c r="XH6">
+        <v>4.93</v>
+      </c>
+      <c r="XI6">
+        <v>26.26</v>
+      </c>
+      <c r="XJ6">
+        <v>13.04</v>
+      </c>
+      <c r="XK6">
+        <v>11.91</v>
+      </c>
+      <c r="XL6">
+        <v>13.49</v>
+      </c>
+      <c r="XM6">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="XN6">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="XO6">
+        <v>11.8</v>
+      </c>
+      <c r="XP6">
+        <v>17.010000000000002</v>
+      </c>
+      <c r="XQ6">
+        <v>17.04</v>
+      </c>
+      <c r="XR6">
+        <v>7.14</v>
+      </c>
+      <c r="XS6">
+        <v>16</v>
+      </c>
+      <c r="XT6">
+        <v>16.77</v>
+      </c>
+      <c r="XU6">
+        <v>11.98</v>
+      </c>
+      <c r="XV6">
+        <v>19.690000000000001</v>
+      </c>
+      <c r="XW6">
+        <v>21.77</v>
+      </c>
+      <c r="XX6">
+        <v>17.47</v>
+      </c>
+      <c r="XY6">
+        <v>18.96</v>
+      </c>
+      <c r="XZ6">
+        <v>14.99</v>
+      </c>
+      <c r="YA6">
+        <v>15.76</v>
+      </c>
+      <c r="YB6">
+        <v>23.77</v>
+      </c>
+      <c r="YC6">
+        <v>15.45</v>
+      </c>
+      <c r="YD6">
+        <v>15.1</v>
+      </c>
+      <c r="YE6">
+        <v>21.49</v>
+      </c>
+      <c r="YF6">
+        <v>18.46</v>
+      </c>
+      <c r="YG6">
+        <v>20.39</v>
+      </c>
+      <c r="YH6">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="YI6">
+        <v>16</v>
+      </c>
+      <c r="YJ6">
+        <v>9.33</v>
+      </c>
+      <c r="YK6">
+        <v>15.73</v>
+      </c>
+      <c r="YL6">
+        <v>6.25</v>
+      </c>
+      <c r="YM6">
+        <v>17.79</v>
+      </c>
+      <c r="YN6">
+        <v>10.38</v>
+      </c>
+      <c r="YO6">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="YP6">
+        <v>26.91</v>
+      </c>
+      <c r="YQ6">
+        <v>8.82</v>
+      </c>
+      <c r="YR6">
+        <v>14.81</v>
+      </c>
+      <c r="YS6">
+        <v>13.64</v>
+      </c>
+      <c r="YT6">
+        <v>8.56</v>
+      </c>
+      <c r="YU6">
+        <v>6.77</v>
+      </c>
+      <c r="YV6">
+        <v>15.58</v>
+      </c>
+      <c r="YW6">
+        <v>15.91</v>
+      </c>
+      <c r="YX6">
+        <v>23.27</v>
+      </c>
+      <c r="YY6">
+        <v>11.27</v>
+      </c>
+      <c r="YZ6">
+        <v>19.48</v>
+      </c>
+      <c r="ZA6">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="ZB6">
+        <v>25.16</v>
+      </c>
+      <c r="ZC6">
+        <v>9.01</v>
+      </c>
+      <c r="ZD6">
+        <v>16.62</v>
+      </c>
+      <c r="ZE6">
+        <v>24.85</v>
+      </c>
+      <c r="ZF6">
+        <v>9.07</v>
+      </c>
+      <c r="ZG6">
+        <v>20.66</v>
+      </c>
+      <c r="ZH6">
+        <v>14.45</v>
+      </c>
+      <c r="ZI6">
+        <v>12.68</v>
+      </c>
+      <c r="ZJ6">
+        <v>26.16</v>
+      </c>
+      <c r="ZK6">
+        <v>14.86</v>
+      </c>
+      <c r="ZL6">
+        <v>15</v>
+      </c>
+      <c r="ZM6">
+        <v>7.35</v>
+      </c>
+      <c r="ZN6">
+        <v>10.66</v>
+      </c>
+      <c r="ZO6">
+        <v>13.7</v>
+      </c>
+      <c r="ZP6">
+        <v>14.49</v>
+      </c>
+      <c r="ZQ6">
+        <v>15.92</v>
+      </c>
+      <c r="ZR6">
+        <v>13.1</v>
+      </c>
+      <c r="ZS6">
+        <v>6.33</v>
+      </c>
+      <c r="ZT6">
+        <v>19.79</v>
+      </c>
+      <c r="ZU6">
+        <v>8.67</v>
+      </c>
+      <c r="ZV6">
+        <v>14.84</v>
+      </c>
+      <c r="ZW6">
+        <v>13.51</v>
+      </c>
+      <c r="ZX6">
+        <v>19.61</v>
+      </c>
+      <c r="ZY6">
+        <v>12.57</v>
+      </c>
+      <c r="ZZ6">
+        <v>15.34</v>
+      </c>
+      <c r="AAA6">
+        <v>16.25</v>
+      </c>
+      <c r="AAB6">
+        <v>12.73</v>
+      </c>
+      <c r="AAC6">
+        <v>20.55</v>
+      </c>
+      <c r="AAD6">
+        <v>10.54</v>
+      </c>
+      <c r="AAE6">
+        <v>26.75</v>
+      </c>
+      <c r="AAF6">
+        <v>11.23</v>
+      </c>
+      <c r="AAG6">
+        <v>15.29</v>
+      </c>
+      <c r="AAH6">
+        <v>12.22</v>
+      </c>
+      <c r="AAI6">
+        <v>15.11</v>
+      </c>
+      <c r="AAJ6">
+        <v>20.59</v>
+      </c>
+      <c r="AAK6">
+        <v>15.81</v>
+      </c>
+      <c r="AAL6">
+        <v>21.92</v>
+      </c>
+      <c r="AAM6">
+        <v>18.12</v>
+      </c>
+      <c r="AAN6">
+        <v>16.36</v>
+      </c>
+      <c r="AAO6">
+        <v>12.97</v>
+      </c>
+      <c r="AAP6">
+        <v>18.48</v>
+      </c>
+      <c r="AAQ6">
+        <v>11.96</v>
+      </c>
+      <c r="AAR6">
+        <v>20.96</v>
+      </c>
+      <c r="AAS6">
+        <v>18.61</v>
+      </c>
+      <c r="AAT6">
+        <v>11.57</v>
+      </c>
+      <c r="AAU6">
+        <v>15.16</v>
+      </c>
+      <c r="AAV6">
+        <v>13.65</v>
+      </c>
+      <c r="AAW6">
+        <v>26.44</v>
+      </c>
+      <c r="AAX6">
+        <v>17.79</v>
+      </c>
+      <c r="AAY6">
+        <v>18.52</v>
+      </c>
+      <c r="AAZ6">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="ABA6">
+        <v>16.940000000000001</v>
+      </c>
+      <c r="ABB6">
+        <v>15.94</v>
+      </c>
+      <c r="ABC6">
+        <v>16.37</v>
+      </c>
+      <c r="ABD6">
+        <v>20.95</v>
+      </c>
+      <c r="ABE6">
+        <v>20.55</v>
+      </c>
+      <c r="ABF6">
+        <v>21.77</v>
+      </c>
+      <c r="ABG6">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="ABH6">
+        <v>21.75</v>
+      </c>
+      <c r="ABI6">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="ABJ6">
+        <v>16.09</v>
+      </c>
+      <c r="ABK6">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="ABL6">
+        <v>11.54</v>
+      </c>
+      <c r="ABM6">
+        <v>17.87</v>
+      </c>
+      <c r="ABN6">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="ABO6">
+        <v>15.5</v>
+      </c>
+      <c r="ABP6">
+        <v>14.46</v>
+      </c>
+      <c r="ABQ6">
+        <v>12.88</v>
+      </c>
+      <c r="ABR6">
+        <v>17.43</v>
+      </c>
+      <c r="ABS6">
+        <v>13.52</v>
+      </c>
+      <c r="ABT6">
+        <v>19.21</v>
+      </c>
+      <c r="ABU6">
+        <v>14.81</v>
+      </c>
+      <c r="ABV6">
+        <v>29.18</v>
+      </c>
+      <c r="ABW6">
+        <v>25.01</v>
+      </c>
+      <c r="ABX6">
+        <v>13.93</v>
+      </c>
+      <c r="ABY6">
+        <v>13.81</v>
+      </c>
+      <c r="ABZ6">
+        <v>8.25</v>
+      </c>
+      <c r="ACA6">
+        <v>13.38</v>
+      </c>
+      <c r="ACB6">
+        <v>18.440000000000001</v>
+      </c>
+      <c r="ACC6">
+        <v>18.190000000000001</v>
+      </c>
+      <c r="ACD6">
+        <v>13.44</v>
+      </c>
+      <c r="ACE6">
+        <v>12.43</v>
+      </c>
+      <c r="ACF6">
         <v>17.579999999999998</v>
       </c>
-      <c r="AX6">
-        <v>41.43</v>
-      </c>
-      <c r="AY6">
-        <v>29.04</v>
-      </c>
-      <c r="AZ6">
-        <v>43.13</v>
-      </c>
-      <c r="BA6">
-        <v>28.45</v>
-      </c>
-      <c r="BB6">
-        <v>32.07</v>
-      </c>
-      <c r="BC6">
-        <v>9.41</v>
-      </c>
-      <c r="BD6">
-        <v>28.05</v>
-      </c>
-      <c r="BE6">
-        <v>33.33</v>
-      </c>
-      <c r="BF6">
-        <v>23.23</v>
-      </c>
-      <c r="BG6">
-        <v>21.75</v>
-      </c>
-      <c r="BH6">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="BI6">
-        <v>27.04</v>
-      </c>
-      <c r="BJ6">
-        <v>29.51</v>
-      </c>
-      <c r="BK6">
-        <v>6.65</v>
-      </c>
-      <c r="BL6">
-        <v>40.369999999999997</v>
-      </c>
-      <c r="BM6">
-        <v>34.159999999999997</v>
-      </c>
-      <c r="BN6">
-        <v>26.57</v>
-      </c>
-      <c r="BO6">
-        <v>14.69</v>
-      </c>
-      <c r="BP6">
-        <v>23.79</v>
-      </c>
-      <c r="BQ6">
-        <v>23.9</v>
-      </c>
-      <c r="BR6">
-        <v>38.200000000000003</v>
-      </c>
-      <c r="BS6">
-        <v>27.62</v>
-      </c>
-      <c r="BT6">
-        <v>5.76</v>
-      </c>
-      <c r="BU6">
-        <v>25.9</v>
-      </c>
-      <c r="BV6">
-        <v>17.3</v>
-      </c>
-      <c r="BW6">
-        <v>27.05</v>
-      </c>
-      <c r="BX6">
-        <v>15.92</v>
-      </c>
-      <c r="BY6">
-        <v>27.78</v>
-      </c>
-      <c r="BZ6">
-        <v>29.24</v>
-      </c>
-      <c r="CA6">
-        <v>24.49</v>
-      </c>
-      <c r="CB6">
-        <v>24.69</v>
-      </c>
-      <c r="CC6">
-        <v>29.51</v>
-      </c>
-      <c r="CD6">
+      <c r="ACG6">
+        <v>21.97</v>
+      </c>
+      <c r="ACH6">
+        <v>19.22</v>
+      </c>
+      <c r="ACI6">
+        <v>13.2</v>
+      </c>
+      <c r="ACJ6">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="ACK6">
+        <v>19.71</v>
+      </c>
+      <c r="ACL6">
+        <v>13.04</v>
+      </c>
+      <c r="ACM6">
+        <v>14.76</v>
+      </c>
+      <c r="ACN6">
+        <v>15.84</v>
+      </c>
+      <c r="ACO6">
+        <v>12.95</v>
+      </c>
+      <c r="ACP6">
+        <v>8.48</v>
+      </c>
+      <c r="ACQ6">
+        <v>4.74</v>
+      </c>
+      <c r="ACR6">
+        <v>21.42</v>
+      </c>
+      <c r="ACS6">
+        <v>15.54</v>
+      </c>
+      <c r="ACT6">
+        <v>15.93</v>
+      </c>
+      <c r="ACU6">
+        <v>10.56</v>
+      </c>
+      <c r="ACV6">
+        <v>7.28</v>
+      </c>
+      <c r="ACW6">
+        <v>14.63</v>
+      </c>
+      <c r="ACX6">
+        <v>15.35</v>
+      </c>
+      <c r="ACY6">
+        <v>12.02</v>
+      </c>
+      <c r="ACZ6">
+        <v>7.75</v>
+      </c>
+      <c r="ADA6">
+        <v>10</v>
+      </c>
+      <c r="ADB6">
+        <v>14.78</v>
+      </c>
+      <c r="ADC6">
+        <v>15.32</v>
+      </c>
+      <c r="ADD6">
+        <v>11.35</v>
+      </c>
+      <c r="ADE6">
+        <v>18.25</v>
+      </c>
+      <c r="ADF6">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="ADG6">
+        <v>13.58</v>
+      </c>
+      <c r="ADH6">
+        <v>15.62</v>
+      </c>
+      <c r="ADI6">
+        <v>14.13</v>
+      </c>
+      <c r="ADJ6">
+        <v>24.12</v>
+      </c>
+      <c r="ADK6">
+        <v>14.61</v>
+      </c>
+      <c r="ADL6">
+        <v>15.44</v>
+      </c>
+      <c r="ADM6">
+        <v>15.99</v>
+      </c>
+      <c r="ADN6">
+        <v>23.84</v>
+      </c>
+      <c r="ADO6">
+        <v>15.69</v>
+      </c>
+      <c r="ADP6">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="ADQ6">
+        <v>14.02</v>
+      </c>
+      <c r="ADR6">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="ADS6">
+        <v>15.12</v>
+      </c>
+      <c r="ADT6">
+        <v>12.3</v>
+      </c>
+      <c r="ADU6">
+        <v>15.3</v>
+      </c>
+      <c r="ADV6">
+        <v>8.39</v>
+      </c>
+      <c r="ADW6">
+        <v>14.28</v>
+      </c>
+      <c r="ADX6">
+        <v>16.28</v>
+      </c>
+      <c r="ADY6">
+        <v>27.85</v>
+      </c>
+      <c r="ADZ6">
+        <v>16.05</v>
+      </c>
+      <c r="AEA6">
+        <v>17.309999999999999</v>
+      </c>
+      <c r="AEB6">
+        <v>16.78</v>
+      </c>
+      <c r="AEC6">
+        <v>24.88</v>
+      </c>
+      <c r="AED6">
+        <v>11.76</v>
+      </c>
+      <c r="AEE6">
+        <v>19.079999999999998</v>
+      </c>
+      <c r="AEF6">
+        <v>14.99</v>
+      </c>
+      <c r="AEG6">
+        <v>11.73</v>
+      </c>
+      <c r="AEH6">
+        <v>21.17</v>
+      </c>
+      <c r="AEI6">
+        <v>22.74</v>
+      </c>
+      <c r="AEJ6">
+        <v>16.260000000000002</v>
+      </c>
+      <c r="AEK6">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="AEL6">
+        <v>20.64</v>
+      </c>
+      <c r="AEM6">
+        <v>21.88</v>
+      </c>
+      <c r="AEN6">
+        <v>24.28</v>
+      </c>
+      <c r="AEO6">
+        <v>21.45</v>
+      </c>
+      <c r="AEP6">
+        <v>10.59</v>
+      </c>
+      <c r="AEQ6">
+        <v>11.39</v>
+      </c>
+      <c r="AER6">
+        <v>18.09</v>
+      </c>
+      <c r="AES6">
+        <v>14.96</v>
+      </c>
+      <c r="AET6">
+        <v>29.97</v>
+      </c>
+      <c r="AEU6">
+        <v>13.01</v>
+      </c>
+      <c r="AEV6">
+        <v>15.5</v>
+      </c>
+      <c r="AEW6">
+        <v>18.97</v>
+      </c>
+      <c r="AEX6">
+        <v>16.440000000000001</v>
+      </c>
+      <c r="AEY6">
+        <v>5.71</v>
+      </c>
+      <c r="AEZ6">
+        <v>19.18</v>
+      </c>
+      <c r="AFA6">
+        <v>24.78</v>
+      </c>
+      <c r="AFB6">
+        <v>9.67</v>
+      </c>
+      <c r="AFC6">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="AFD6">
+        <v>15.68</v>
+      </c>
+      <c r="AFE6">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="AFF6">
+        <v>7.99</v>
+      </c>
+      <c r="AFG6">
+        <v>30.63</v>
+      </c>
+      <c r="AFH6">
+        <v>17.03</v>
+      </c>
+      <c r="AFI6">
+        <v>19.45</v>
+      </c>
+      <c r="AFJ6">
+        <v>13.85</v>
+      </c>
+      <c r="AFK6">
+        <v>31.09</v>
+      </c>
+      <c r="AFL6">
+        <v>15.06</v>
+      </c>
+      <c r="AFM6">
+        <v>18.43</v>
+      </c>
+      <c r="AFN6">
+        <v>17.079999999999998</v>
+      </c>
+      <c r="AFO6">
+        <v>15.2</v>
+      </c>
+      <c r="AFP6">
+        <v>25.16</v>
+      </c>
+      <c r="AFQ6">
+        <v>11.45</v>
+      </c>
+      <c r="AFR6">
+        <v>14.4</v>
+      </c>
+      <c r="AFS6">
+        <v>24.66</v>
+      </c>
+      <c r="AFT6">
+        <v>5.48</v>
+      </c>
+      <c r="AFU6">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="AFV6">
+        <v>17.440000000000001</v>
+      </c>
+      <c r="AFW6">
+        <v>21.68</v>
+      </c>
+      <c r="AFX6">
+        <v>13.87</v>
+      </c>
+      <c r="AFY6">
+        <v>11</v>
+      </c>
+      <c r="AFZ6">
+        <v>9.67</v>
+      </c>
+      <c r="AGA6">
+        <v>5.68</v>
+      </c>
+      <c r="AGB6">
+        <v>15.14</v>
+      </c>
+      <c r="AGC6">
+        <v>19.920000000000002</v>
+      </c>
+      <c r="AGD6">
         <v>15.64</v>
       </c>
-      <c r="CE6">
-        <v>30.78</v>
-      </c>
-      <c r="CF6">
-        <v>41.09</v>
-      </c>
-      <c r="CG6">
-        <v>23.88</v>
-      </c>
-      <c r="CH6">
-        <v>26.61</v>
-      </c>
-      <c r="CI6">
-        <v>23.76</v>
-      </c>
-      <c r="CJ6">
-        <v>27.69</v>
-      </c>
-      <c r="CK6">
-        <v>45.28</v>
-      </c>
-      <c r="CL6">
-        <v>26.71</v>
-      </c>
-      <c r="CM6">
-        <v>32.979999999999997</v>
-      </c>
-      <c r="CN6">
-        <v>36.86</v>
-      </c>
-      <c r="CO6">
-        <v>27.38</v>
-      </c>
-      <c r="CP6">
-        <v>24.82</v>
-      </c>
-      <c r="CQ6">
-        <v>24.41</v>
-      </c>
-      <c r="CR6">
-        <v>4.05</v>
-      </c>
-      <c r="CS6">
-        <v>22.23</v>
-      </c>
-      <c r="CT6">
-        <v>9.27</v>
-      </c>
-      <c r="CU6">
-        <v>31.69</v>
-      </c>
-      <c r="CV6">
-        <v>20.49</v>
-      </c>
-      <c r="CW6">
-        <v>29.43</v>
-      </c>
-      <c r="CX6">
-        <v>4.79</v>
-      </c>
-      <c r="CY6">
-        <v>34.369999999999997</v>
-      </c>
-      <c r="CZ6">
-        <v>15.74</v>
-      </c>
-      <c r="DA6">
-        <v>40.130000000000003</v>
-      </c>
-      <c r="DB6">
-        <v>26.01</v>
-      </c>
-      <c r="DC6">
-        <v>22.45</v>
-      </c>
-      <c r="DD6">
-        <v>28.57</v>
-      </c>
-      <c r="DE6">
-        <v>29.27</v>
-      </c>
-      <c r="DF6">
-        <v>33.479999999999997</v>
-      </c>
-      <c r="DG6">
-        <v>18.84</v>
-      </c>
-      <c r="DH6">
-        <v>20.21</v>
-      </c>
-      <c r="DI6">
-        <v>27.79</v>
-      </c>
-      <c r="DJ6">
-        <v>13.9</v>
-      </c>
-      <c r="DK6">
-        <v>32.520000000000003</v>
-      </c>
-      <c r="DL6">
-        <v>6.03</v>
-      </c>
-      <c r="DM6">
-        <v>8.93</v>
-      </c>
-      <c r="DN6">
-        <v>9.4700000000000006</v>
-      </c>
-      <c r="DO6">
-        <v>30.94</v>
-      </c>
-      <c r="DP6">
-        <v>22.73</v>
-      </c>
-      <c r="DQ6">
-        <v>25.86</v>
-      </c>
-      <c r="DR6">
-        <v>23.79</v>
-      </c>
-      <c r="DS6">
-        <v>20.76</v>
-      </c>
-      <c r="DT6">
-        <v>30.9</v>
-      </c>
-      <c r="DU6">
-        <v>27.82</v>
-      </c>
-      <c r="DV6">
-        <v>29.24</v>
-      </c>
-      <c r="DW6">
-        <v>39.56</v>
-      </c>
-      <c r="DX6">
-        <v>29.75</v>
-      </c>
-      <c r="DY6">
-        <v>21.26</v>
-      </c>
-      <c r="DZ6">
-        <v>27.02</v>
-      </c>
-      <c r="EA6">
-        <v>22.73</v>
-      </c>
-      <c r="EB6">
-        <v>27.36</v>
-      </c>
-      <c r="EC6">
-        <v>26</v>
-      </c>
-      <c r="ED6">
-        <v>18.84</v>
-      </c>
-      <c r="EE6">
-        <v>19.829999999999998</v>
-      </c>
-      <c r="EF6">
-        <v>28.74</v>
-      </c>
-      <c r="EG6">
-        <v>34.33</v>
-      </c>
-      <c r="EH6">
-        <v>30.63</v>
-      </c>
-      <c r="EI6">
-        <v>28.08</v>
-      </c>
-      <c r="EJ6">
-        <v>31.14</v>
-      </c>
-      <c r="EK6">
-        <v>24.72</v>
-      </c>
-      <c r="EL6">
-        <v>23.23</v>
-      </c>
-      <c r="EM6">
-        <v>38.450000000000003</v>
-      </c>
-      <c r="EN6">
-        <v>24.69</v>
-      </c>
-      <c r="EO6">
-        <v>29.65</v>
-      </c>
-      <c r="EP6">
-        <v>26.81</v>
-      </c>
-      <c r="EQ6">
-        <v>39.090000000000003</v>
-      </c>
-      <c r="ER6">
-        <v>30.32</v>
-      </c>
-      <c r="ES6">
-        <v>24.93</v>
-      </c>
-      <c r="ET6">
-        <v>24.54</v>
-      </c>
-      <c r="EU6">
-        <v>28.41</v>
-      </c>
-      <c r="EV6">
-        <v>41.57</v>
-      </c>
-      <c r="EW6">
-        <v>28.04</v>
-      </c>
-      <c r="EX6">
-        <v>19.260000000000002</v>
-      </c>
-      <c r="EY6">
-        <v>29.87</v>
-      </c>
-      <c r="EZ6">
-        <v>24.71</v>
-      </c>
-      <c r="FA6">
-        <v>21.85</v>
-      </c>
-      <c r="FB6">
-        <v>32.369999999999997</v>
-      </c>
-      <c r="FC6">
-        <v>7.18</v>
-      </c>
-      <c r="FD6">
-        <v>23.83</v>
-      </c>
-      <c r="FE6">
-        <v>20.079999999999998</v>
-      </c>
-      <c r="FF6">
-        <v>33.03</v>
-      </c>
-      <c r="FG6">
-        <v>28.24</v>
-      </c>
-      <c r="FH6">
-        <v>28.53</v>
-      </c>
-      <c r="FI6">
-        <v>25.3</v>
-      </c>
-      <c r="FJ6">
-        <v>24.87</v>
-      </c>
-      <c r="FK6">
-        <v>32.24</v>
-      </c>
-      <c r="FL6">
-        <v>29.08</v>
-      </c>
-      <c r="FM6">
-        <v>31.02</v>
-      </c>
-      <c r="FN6">
-        <v>32.39</v>
-      </c>
-      <c r="FO6">
-        <v>30.9</v>
-      </c>
-      <c r="FP6">
-        <v>34</v>
-      </c>
-      <c r="FQ6">
-        <v>24.34</v>
-      </c>
-      <c r="FR6">
-        <v>31.82</v>
-      </c>
-      <c r="FS6">
-        <v>37.869999999999997</v>
-      </c>
-      <c r="FT6">
-        <v>33.99</v>
-      </c>
-      <c r="FU6">
-        <v>4.08</v>
-      </c>
-      <c r="FV6">
-        <v>31.01</v>
-      </c>
-      <c r="FW6">
-        <v>31.11</v>
-      </c>
-      <c r="FX6">
-        <v>27.88</v>
-      </c>
-      <c r="FY6">
-        <v>29.17</v>
-      </c>
-      <c r="FZ6">
-        <v>23.44</v>
-      </c>
-      <c r="GA6">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="GB6">
-        <v>20.5</v>
-      </c>
-      <c r="GC6">
-        <v>26.85</v>
-      </c>
-      <c r="GD6">
-        <v>23.34</v>
-      </c>
-      <c r="GE6">
-        <v>6.4</v>
-      </c>
-      <c r="GF6">
-        <v>26.85</v>
-      </c>
-      <c r="GG6">
-        <v>4.71</v>
-      </c>
-      <c r="GH6">
-        <v>24.55</v>
-      </c>
-      <c r="GI6">
-        <v>25.67</v>
-      </c>
-      <c r="GJ6">
-        <v>20.51</v>
-      </c>
-      <c r="GK6">
-        <v>27.72</v>
-      </c>
-      <c r="GL6">
-        <v>27.63</v>
-      </c>
-      <c r="GM6">
-        <v>25.73</v>
-      </c>
-      <c r="GN6">
-        <v>29.13</v>
-      </c>
-      <c r="GO6">
-        <v>25.39</v>
-      </c>
-      <c r="GP6">
-        <v>28.77</v>
-      </c>
-      <c r="GQ6">
-        <v>19.82</v>
-      </c>
-      <c r="GR6">
-        <v>13.6</v>
-      </c>
-      <c r="GS6">
-        <v>31.92</v>
-      </c>
-      <c r="GT6">
-        <v>21.05</v>
-      </c>
-      <c r="GU6">
-        <v>26.47</v>
-      </c>
-      <c r="GV6">
-        <v>6.52</v>
-      </c>
-      <c r="GW6">
-        <v>34.82</v>
-      </c>
-      <c r="GX6">
-        <v>29.32</v>
-      </c>
-      <c r="GY6">
-        <v>33.19</v>
-      </c>
-      <c r="GZ6">
-        <v>26.33</v>
-      </c>
-      <c r="HA6">
-        <v>6.62</v>
-      </c>
-      <c r="HB6">
-        <v>4.1399999999999997</v>
-      </c>
-      <c r="HC6">
-        <v>26.7</v>
-      </c>
-      <c r="HD6">
-        <v>40.909999999999997</v>
-      </c>
-      <c r="HE6">
-        <v>22.95</v>
-      </c>
-      <c r="HF6">
-        <v>21.15</v>
-      </c>
-      <c r="HG6">
-        <v>19.11</v>
-      </c>
-      <c r="HH6">
-        <v>6.33</v>
-      </c>
-      <c r="HI6">
-        <v>21.21</v>
-      </c>
-      <c r="HJ6">
-        <v>30.32</v>
-      </c>
-      <c r="HK6">
-        <v>19.98</v>
-      </c>
-      <c r="HL6">
-        <v>21.14</v>
-      </c>
-      <c r="HM6">
-        <v>34.25</v>
-      </c>
-      <c r="HN6">
-        <v>23.31</v>
-      </c>
-      <c r="HO6">
-        <v>23.23</v>
-      </c>
-      <c r="HP6">
-        <v>35.31</v>
-      </c>
-      <c r="HQ6">
-        <v>25.54</v>
-      </c>
-      <c r="HR6">
-        <v>18.03</v>
-      </c>
-      <c r="HS6">
-        <v>27.29</v>
-      </c>
-      <c r="HT6">
-        <v>28.95</v>
-      </c>
-      <c r="HU6">
-        <v>24.07</v>
-      </c>
-      <c r="HV6">
-        <v>29.13</v>
-      </c>
-      <c r="HW6">
-        <v>29.18</v>
-      </c>
-      <c r="HX6">
-        <v>24.79</v>
-      </c>
-      <c r="HY6">
-        <v>32.44</v>
-      </c>
-      <c r="HZ6">
-        <v>36.409999999999997</v>
-      </c>
-      <c r="IA6">
-        <v>29.83</v>
-      </c>
-      <c r="IB6">
-        <v>10.77</v>
-      </c>
-      <c r="IC6">
-        <v>20.149999999999999</v>
-      </c>
-      <c r="ID6">
-        <v>42.22</v>
-      </c>
-      <c r="IE6">
-        <v>32.549999999999997</v>
-      </c>
-      <c r="IF6">
-        <v>22.37</v>
-      </c>
-      <c r="IG6">
-        <v>28.29</v>
-      </c>
-      <c r="IH6">
-        <v>37.15</v>
-      </c>
-      <c r="II6">
-        <v>19.62</v>
-      </c>
-      <c r="IJ6">
-        <v>23.27</v>
-      </c>
-      <c r="IK6">
-        <v>27.67</v>
-      </c>
-      <c r="IL6">
-        <v>14.99</v>
-      </c>
-      <c r="IM6">
-        <v>30.59</v>
-      </c>
-      <c r="IN6">
-        <v>25.17</v>
-      </c>
-      <c r="IO6">
-        <v>16.72</v>
-      </c>
-      <c r="IP6">
-        <v>19.63</v>
-      </c>
-      <c r="IQ6">
-        <v>23.82</v>
-      </c>
-      <c r="IR6">
-        <v>21.85</v>
-      </c>
-      <c r="IS6">
-        <v>24.6</v>
-      </c>
-      <c r="IT6">
-        <v>26.99</v>
-      </c>
-      <c r="IU6">
-        <v>21.72</v>
-      </c>
-      <c r="IV6">
-        <v>21.87</v>
-      </c>
-      <c r="IW6">
-        <v>25.72</v>
-      </c>
-      <c r="IX6">
-        <v>21</v>
-      </c>
-      <c r="IY6">
-        <v>28.61</v>
-      </c>
-      <c r="IZ6">
-        <v>25.64</v>
-      </c>
-      <c r="JA6">
-        <v>24.93</v>
-      </c>
-      <c r="JB6">
-        <v>23.8</v>
-      </c>
-      <c r="JC6">
-        <v>23.32</v>
-      </c>
-      <c r="JD6">
-        <v>33.53</v>
-      </c>
-      <c r="JE6">
-        <v>30.65</v>
-      </c>
-      <c r="JF6">
-        <v>24.74</v>
-      </c>
-      <c r="JG6">
+      <c r="AGE6">
+        <v>15.91</v>
+      </c>
+      <c r="AGF6">
+        <v>15.9</v>
+      </c>
+      <c r="AGG6">
+        <v>18.010000000000002</v>
+      </c>
+      <c r="AGH6">
+        <v>8.9</v>
+      </c>
+      <c r="AGI6">
+        <v>12.63</v>
+      </c>
+      <c r="AGJ6">
+        <v>16</v>
+      </c>
+      <c r="AGK6">
+        <v>11.99</v>
+      </c>
+      <c r="AGL6">
+        <v>15.05</v>
+      </c>
+      <c r="AGM6">
+        <v>12.63</v>
+      </c>
+      <c r="AGN6">
+        <v>16.37</v>
+      </c>
+      <c r="AGO6">
+        <v>9</v>
+      </c>
+      <c r="AGP6">
+        <v>14.23</v>
+      </c>
+      <c r="AGQ6">
+        <v>19.84</v>
+      </c>
+      <c r="AGR6">
+        <v>17.09</v>
+      </c>
+      <c r="AGS6">
+        <v>18.05</v>
+      </c>
+      <c r="AGT6">
+        <v>11.93</v>
+      </c>
+      <c r="AGU6">
+        <v>13.54</v>
+      </c>
+      <c r="AGV6">
+        <v>17.36</v>
+      </c>
+      <c r="AGW6">
+        <v>9.99</v>
+      </c>
+      <c r="AGX6">
+        <v>15.19</v>
+      </c>
+      <c r="AGY6">
+        <v>18.97</v>
+      </c>
+      <c r="AGZ6">
+        <v>11.8</v>
+      </c>
+      <c r="AHA6">
+        <v>6.49</v>
+      </c>
+      <c r="AHB6">
+        <v>20.37</v>
+      </c>
+      <c r="AHC6">
+        <v>21.36</v>
+      </c>
+      <c r="AHD6">
+        <v>15.41</v>
+      </c>
+      <c r="AHE6">
+        <v>11.73</v>
+      </c>
+      <c r="AHF6">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="AHG6">
+        <v>19.7</v>
+      </c>
+      <c r="AHH6">
+        <v>13.64</v>
+      </c>
+      <c r="AHI6">
+        <v>14.56</v>
+      </c>
+      <c r="AHJ6">
+        <v>15.8</v>
+      </c>
+      <c r="AHK6">
+        <v>18.940000000000001</v>
+      </c>
+      <c r="AHL6">
+        <v>20.25</v>
+      </c>
+      <c r="AHM6">
+        <v>15.78</v>
+      </c>
+      <c r="AHN6">
+        <v>20.190000000000001</v>
+      </c>
+      <c r="AHO6">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="AHP6">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="AHQ6">
+        <v>13.64</v>
+      </c>
+      <c r="AHR6">
+        <v>22.93</v>
+      </c>
+      <c r="AHS6">
+        <v>12.85</v>
+      </c>
+      <c r="AHT6">
+        <v>15.62</v>
+      </c>
+      <c r="AHU6">
+        <v>15.17</v>
+      </c>
+      <c r="AHV6">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AHW6">
+        <v>16.62</v>
+      </c>
+      <c r="AHX6">
+        <v>10.26</v>
+      </c>
+      <c r="AHY6">
+        <v>11.4</v>
+      </c>
+      <c r="AHZ6">
+        <v>13.36</v>
+      </c>
+      <c r="AIA6">
+        <v>15.35</v>
+      </c>
+      <c r="AIB6">
+        <v>14.61</v>
+      </c>
+      <c r="AIC6">
+        <v>10.89</v>
+      </c>
+      <c r="AID6">
         <v>22.62</v>
       </c>
-      <c r="JH6">
-        <v>3.68</v>
-      </c>
-      <c r="JI6">
-        <v>33.340000000000003</v>
-      </c>
-      <c r="JJ6">
-        <v>23.19</v>
-      </c>
-      <c r="JK6">
-        <v>28.61</v>
-      </c>
-      <c r="JL6">
-        <v>14.79</v>
-      </c>
-      <c r="JM6">
-        <v>3.97</v>
-      </c>
-      <c r="JN6">
-        <v>32.01</v>
-      </c>
-      <c r="JO6">
-        <v>18.88</v>
-      </c>
-      <c r="JP6">
-        <v>30.91</v>
-      </c>
-      <c r="JQ6">
-        <v>24.81</v>
-      </c>
-      <c r="JR6">
-        <v>23.85</v>
-      </c>
-      <c r="JS6">
-        <v>29.37</v>
-      </c>
-      <c r="JT6">
-        <v>22.49</v>
-      </c>
-      <c r="JU6">
-        <v>17.670000000000002</v>
-      </c>
-      <c r="JV6">
-        <v>21.92</v>
-      </c>
-      <c r="JW6">
-        <v>21.17</v>
-      </c>
-      <c r="JX6">
-        <v>22.05</v>
-      </c>
-      <c r="JY6">
-        <v>27.19</v>
-      </c>
-      <c r="JZ6">
-        <v>33.07</v>
-      </c>
-      <c r="KA6">
-        <v>37</v>
-      </c>
-      <c r="KB6">
-        <v>33.549999999999997</v>
-      </c>
-      <c r="KC6">
-        <v>18.920000000000002</v>
-      </c>
-      <c r="KD6">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="KE6">
-        <v>26.96</v>
-      </c>
-      <c r="KF6">
-        <v>37.83</v>
-      </c>
-      <c r="KG6">
-        <v>28.17</v>
-      </c>
-      <c r="KH6">
-        <v>30.38</v>
-      </c>
-      <c r="KI6">
-        <v>18.82</v>
-      </c>
-      <c r="KJ6">
-        <v>28.21</v>
-      </c>
-      <c r="KK6">
-        <v>32.369999999999997</v>
-      </c>
-      <c r="KL6">
-        <v>25.06</v>
-      </c>
-      <c r="KM6">
-        <v>30.16</v>
-      </c>
-      <c r="KN6">
-        <v>33.78</v>
-      </c>
-      <c r="KO6">
-        <v>10.6</v>
-      </c>
-      <c r="KP6">
-        <v>34.53</v>
-      </c>
-      <c r="KQ6">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="KR6">
-        <v>31.62</v>
-      </c>
-      <c r="KS6">
-        <v>26.14</v>
-      </c>
-      <c r="KT6">
-        <v>26.7</v>
-      </c>
-      <c r="KU6">
-        <v>18.579999999999998</v>
-      </c>
-      <c r="KV6">
-        <v>18.87</v>
-      </c>
-      <c r="KW6">
-        <v>26.53</v>
-      </c>
-      <c r="KX6">
-        <v>26.84</v>
-      </c>
-      <c r="KY6">
-        <v>38.6</v>
-      </c>
-      <c r="KZ6">
-        <v>13.78</v>
-      </c>
-      <c r="LA6">
-        <v>22.96</v>
-      </c>
-      <c r="LB6">
-        <v>30.39</v>
-      </c>
-      <c r="LC6">
-        <v>24.79</v>
-      </c>
-      <c r="LD6">
-        <v>40.58</v>
-      </c>
-      <c r="LE6">
-        <v>35.47</v>
-      </c>
-      <c r="LF6">
-        <v>29.68</v>
-      </c>
-      <c r="LG6">
-        <v>24.52</v>
-      </c>
-      <c r="LH6">
-        <v>42.53</v>
-      </c>
-      <c r="LI6">
-        <v>31.26</v>
-      </c>
-      <c r="LJ6">
-        <v>11.32</v>
-      </c>
-      <c r="LK6">
-        <v>28.19</v>
-      </c>
-      <c r="LL6">
-        <v>26.69</v>
-      </c>
-      <c r="LM6">
-        <v>26.32</v>
-      </c>
-      <c r="LN6">
-        <v>27.23</v>
-      </c>
-      <c r="LO6">
-        <v>32.64</v>
-      </c>
-      <c r="LP6">
-        <v>38.020000000000003</v>
-      </c>
-      <c r="LQ6">
-        <v>27.91</v>
-      </c>
-      <c r="LR6">
-        <v>44.59</v>
-      </c>
-      <c r="LS6">
-        <v>26.58</v>
-      </c>
-      <c r="LT6">
-        <v>19.39</v>
-      </c>
-      <c r="LU6">
-        <v>28.6</v>
-      </c>
-      <c r="LV6">
-        <v>46.92</v>
-      </c>
-      <c r="LW6">
-        <v>25.34</v>
-      </c>
-      <c r="LX6">
-        <v>25.54</v>
-      </c>
-      <c r="LY6">
-        <v>6.73</v>
-      </c>
-      <c r="LZ6">
-        <v>15.53</v>
-      </c>
-      <c r="MA6">
-        <v>29.04</v>
-      </c>
-      <c r="MB6">
-        <v>28.66</v>
-      </c>
-      <c r="MC6">
-        <v>31.11</v>
-      </c>
-      <c r="MD6">
-        <v>27.03</v>
-      </c>
-      <c r="ME6">
-        <v>36.74</v>
-      </c>
-      <c r="MF6">
-        <v>21.28</v>
-      </c>
-      <c r="MG6">
-        <v>27.96</v>
-      </c>
-      <c r="MH6">
-        <v>35.72</v>
-      </c>
-      <c r="MI6">
-        <v>31.64</v>
-      </c>
-      <c r="MJ6">
-        <v>21.05</v>
-      </c>
-      <c r="MK6">
-        <v>23.01</v>
-      </c>
-      <c r="ML6">
-        <v>45.66</v>
-      </c>
-      <c r="MM6">
-        <v>30.39</v>
-      </c>
-      <c r="MN6">
-        <v>23.67</v>
-      </c>
-      <c r="MO6">
-        <v>30.82</v>
-      </c>
-      <c r="MP6">
-        <v>34.33</v>
-      </c>
-      <c r="MQ6">
-        <v>27.38</v>
-      </c>
-      <c r="MR6">
-        <v>31.02</v>
-      </c>
-      <c r="MS6">
-        <v>28.35</v>
-      </c>
-      <c r="MT6">
-        <v>35.14</v>
-      </c>
-      <c r="MU6">
-        <v>28.42</v>
-      </c>
-      <c r="MV6">
-        <v>20.28</v>
-      </c>
-      <c r="MW6">
-        <v>27.73</v>
-      </c>
-      <c r="MX6">
-        <v>33.03</v>
-      </c>
-      <c r="MY6">
-        <v>26.78</v>
-      </c>
-      <c r="MZ6">
-        <v>14.22</v>
-      </c>
-      <c r="NA6">
-        <v>18.71</v>
-      </c>
-      <c r="NB6">
-        <v>31.66</v>
-      </c>
-      <c r="NC6">
-        <v>26.33</v>
-      </c>
-      <c r="ND6">
-        <v>25.93</v>
-      </c>
-      <c r="NE6">
-        <v>25.33</v>
-      </c>
-      <c r="NF6">
-        <v>29.43</v>
-      </c>
-      <c r="NG6">
-        <v>28.49</v>
-      </c>
-      <c r="NH6">
-        <v>24.41</v>
-      </c>
-      <c r="NI6">
-        <v>24.32</v>
-      </c>
-      <c r="NJ6">
-        <v>33.97</v>
-      </c>
-      <c r="NK6">
-        <v>14.53</v>
-      </c>
-      <c r="NL6">
-        <v>24.42</v>
-      </c>
-      <c r="NM6">
-        <v>26.49</v>
-      </c>
-      <c r="NN6">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="NO6">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="NP6">
-        <v>30.14</v>
-      </c>
-      <c r="NQ6">
-        <v>24.19</v>
-      </c>
-      <c r="NR6">
-        <v>31.34</v>
-      </c>
-      <c r="NS6">
+      <c r="AIE6">
+        <v>17.45</v>
+      </c>
+      <c r="AIF6">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="AIG6">
+        <v>22.36</v>
+      </c>
+      <c r="AIH6">
+        <v>11.76</v>
+      </c>
+      <c r="AII6">
+        <v>8.27</v>
+      </c>
+      <c r="AIJ6">
+        <v>17.61</v>
+      </c>
+      <c r="AIK6">
+        <v>12.03</v>
+      </c>
+      <c r="AIL6">
+        <v>12.14</v>
+      </c>
+      <c r="AIM6">
+        <v>7.29</v>
+      </c>
+      <c r="AIN6">
+        <v>19.809999999999999</v>
+      </c>
+      <c r="AIO6">
+        <v>15.5</v>
+      </c>
+      <c r="AIP6">
+        <v>14.29</v>
+      </c>
+      <c r="AIQ6">
+        <v>18.02</v>
+      </c>
+      <c r="AIR6">
+        <v>14.96</v>
+      </c>
+      <c r="AIS6">
+        <v>13.49</v>
+      </c>
+      <c r="AIT6">
         <v>17.66</v>
       </c>
-      <c r="NT6">
-        <v>21.43</v>
-      </c>
-      <c r="NU6">
-        <v>32.840000000000003</v>
-      </c>
-      <c r="NV6">
-        <v>28.74</v>
-      </c>
-      <c r="NW6">
-        <v>26.43</v>
-      </c>
-      <c r="NX6">
-        <v>24.12</v>
-      </c>
-      <c r="NY6">
-        <v>24.95</v>
-      </c>
-      <c r="NZ6">
-        <v>9.7799999999999994</v>
-      </c>
-      <c r="OA6">
-        <v>35.479999999999997</v>
-      </c>
-      <c r="OB6">
-        <v>24.46</v>
-      </c>
-      <c r="OC6">
-        <v>20.52</v>
-      </c>
-      <c r="OD6">
-        <v>33</v>
-      </c>
-      <c r="OE6">
-        <v>32.590000000000003</v>
-      </c>
-      <c r="OF6">
-        <v>22.77</v>
-      </c>
-      <c r="OG6">
-        <v>20.65</v>
-      </c>
-      <c r="OH6">
-        <v>27.76</v>
-      </c>
-      <c r="OI6">
-        <v>33.840000000000003</v>
-      </c>
-      <c r="OJ6">
-        <v>30.18</v>
-      </c>
-      <c r="OK6">
-        <v>8.9600000000000009</v>
-      </c>
-      <c r="OL6">
-        <v>28.55</v>
-      </c>
-      <c r="OM6">
-        <v>6.89</v>
-      </c>
-      <c r="ON6">
-        <v>27.78</v>
-      </c>
-      <c r="OO6">
-        <v>30.98</v>
-      </c>
-      <c r="OP6">
-        <v>26.69</v>
-      </c>
-      <c r="OQ6">
-        <v>35.630000000000003</v>
-      </c>
-      <c r="OR6">
-        <v>32.75</v>
-      </c>
-      <c r="OS6">
-        <v>31.88</v>
-      </c>
-      <c r="OT6">
-        <v>7.83</v>
-      </c>
-      <c r="OU6">
-        <v>41.98</v>
-      </c>
-      <c r="OV6">
-        <v>25.57</v>
-      </c>
-      <c r="OW6">
-        <v>38.19</v>
-      </c>
-      <c r="OX6">
-        <v>29.96</v>
-      </c>
-      <c r="OY6">
-        <v>26.02</v>
-      </c>
-      <c r="OZ6">
-        <v>34.520000000000003</v>
-      </c>
-      <c r="PA6">
-        <v>25.03</v>
-      </c>
-      <c r="PB6">
-        <v>22.37</v>
-      </c>
-      <c r="PC6">
-        <v>27.54</v>
-      </c>
-      <c r="PD6">
-        <v>6.09</v>
-      </c>
-      <c r="PE6">
-        <v>21.07</v>
-      </c>
-      <c r="PF6">
-        <v>35.090000000000003</v>
-      </c>
-      <c r="PG6">
-        <v>20.68</v>
-      </c>
-      <c r="PH6">
-        <v>41.99</v>
-      </c>
-      <c r="PI6">
-        <v>28.73</v>
-      </c>
-      <c r="PJ6">
-        <v>19.68</v>
-      </c>
-      <c r="PK6">
-        <v>22.62</v>
-      </c>
-      <c r="PL6">
-        <v>21.23</v>
-      </c>
-      <c r="PM6">
-        <v>18.11</v>
-      </c>
-      <c r="PN6">
-        <v>16.78</v>
-      </c>
-      <c r="PO6">
-        <v>22.3</v>
-      </c>
-      <c r="PP6">
-        <v>26.89</v>
-      </c>
-      <c r="PQ6">
-        <v>26.53</v>
-      </c>
-      <c r="PR6">
-        <v>33.86</v>
-      </c>
-      <c r="PS6">
-        <v>30.28</v>
-      </c>
-      <c r="PT6">
-        <v>30.99</v>
-      </c>
-      <c r="PU6">
-        <v>6.62</v>
-      </c>
-      <c r="PV6">
-        <v>28.58</v>
-      </c>
-      <c r="PW6">
-        <v>36.99</v>
-      </c>
-      <c r="PX6">
-        <v>20.12</v>
-      </c>
-      <c r="PY6">
-        <v>31.81</v>
-      </c>
-      <c r="PZ6">
-        <v>25.59</v>
-      </c>
-      <c r="QA6">
-        <v>33.69</v>
-      </c>
-      <c r="QB6">
-        <v>7.96</v>
-      </c>
-      <c r="QC6">
-        <v>41.57</v>
-      </c>
-      <c r="QD6">
-        <v>24.69</v>
-      </c>
-      <c r="QE6">
-        <v>29.98</v>
-      </c>
-      <c r="QF6">
-        <v>35.32</v>
-      </c>
-      <c r="QG6">
-        <v>24.29</v>
-      </c>
-      <c r="QH6">
-        <v>28.87</v>
-      </c>
-      <c r="QI6">
-        <v>35.97</v>
-      </c>
-      <c r="QJ6">
-        <v>6.23</v>
-      </c>
-      <c r="QK6">
-        <v>27.36</v>
-      </c>
-      <c r="QL6">
-        <v>26.15</v>
-      </c>
-      <c r="QM6">
-        <v>31.85</v>
-      </c>
-      <c r="QN6">
-        <v>30.29</v>
-      </c>
-      <c r="QO6">
-        <v>25.38</v>
-      </c>
-      <c r="QP6">
-        <v>27.48</v>
-      </c>
-      <c r="QQ6">
-        <v>30.38</v>
-      </c>
-      <c r="QR6">
-        <v>26.07</v>
-      </c>
-      <c r="QS6">
-        <v>32.92</v>
-      </c>
-      <c r="QT6">
-        <v>5.96</v>
-      </c>
-      <c r="QU6">
-        <v>20.21</v>
-      </c>
-      <c r="QV6">
-        <v>29.49</v>
-      </c>
-      <c r="QW6">
-        <v>22.31</v>
-      </c>
-      <c r="QX6">
-        <v>25.58</v>
-      </c>
-      <c r="QY6">
-        <v>14.19</v>
-      </c>
-      <c r="QZ6">
-        <v>34.659999999999997</v>
-      </c>
-      <c r="RA6">
-        <v>29.85</v>
-      </c>
-      <c r="RB6">
-        <v>12.47</v>
-      </c>
-      <c r="RC6">
-        <v>13.84</v>
-      </c>
-      <c r="RD6">
-        <v>23.11</v>
-      </c>
-      <c r="RE6">
-        <v>35.17</v>
-      </c>
-      <c r="RF6">
-        <v>32.46</v>
-      </c>
-      <c r="RG6">
-        <v>32.909999999999997</v>
-      </c>
-      <c r="RH6">
-        <v>7.08</v>
-      </c>
-      <c r="RI6">
-        <v>33.6</v>
-      </c>
-      <c r="RJ6">
-        <v>25.84</v>
-      </c>
-      <c r="RK6">
-        <v>23.81</v>
-      </c>
-      <c r="RL6">
-        <v>3.93</v>
-      </c>
-      <c r="RM6">
-        <v>42.41</v>
-      </c>
-      <c r="RN6">
-        <v>32.090000000000003</v>
-      </c>
-      <c r="RO6">
-        <v>26.83</v>
-      </c>
-      <c r="RP6">
-        <v>39.92</v>
-      </c>
-      <c r="RQ6">
-        <v>33.76</v>
-      </c>
-      <c r="RR6">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="RS6">
-        <v>27.36</v>
-      </c>
-      <c r="RT6">
-        <v>26.01</v>
-      </c>
-      <c r="RU6">
-        <v>23.65</v>
-      </c>
-      <c r="RV6">
+      <c r="AIU6">
+        <v>11.46</v>
+      </c>
+      <c r="AIV6">
+        <v>7.32</v>
+      </c>
+      <c r="AIW6">
+        <v>19.41</v>
+      </c>
+      <c r="AIX6">
+        <v>12.36</v>
+      </c>
+      <c r="AIY6">
+        <v>11.42</v>
+      </c>
+      <c r="AIZ6">
+        <v>13.75</v>
+      </c>
+      <c r="AJA6">
+        <v>15.14</v>
+      </c>
+      <c r="AJB6">
+        <v>18.32</v>
+      </c>
+      <c r="AJC6">
+        <v>15.68</v>
+      </c>
+      <c r="AJD6">
+        <v>19.89</v>
+      </c>
+      <c r="AJE6">
+        <v>16.87</v>
+      </c>
+      <c r="AJF6">
+        <v>23.74</v>
+      </c>
+      <c r="AJG6">
+        <v>8.26</v>
+      </c>
+      <c r="AJH6">
+        <v>25.04</v>
+      </c>
+      <c r="AJI6">
+        <v>17.37</v>
+      </c>
+      <c r="AJJ6">
+        <v>18.170000000000002</v>
+      </c>
+      <c r="AJK6">
+        <v>11.64</v>
+      </c>
+      <c r="AJL6">
+        <v>11.95</v>
+      </c>
+      <c r="AJM6">
+        <v>11.97</v>
+      </c>
+      <c r="AJN6">
+        <v>13.77</v>
+      </c>
+      <c r="AJO6">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="AJP6">
+        <v>14.82</v>
+      </c>
+      <c r="AJQ6">
+        <v>15.32</v>
+      </c>
+      <c r="AJR6">
+        <v>16.7</v>
+      </c>
+      <c r="AJS6">
+        <v>15.14</v>
+      </c>
+      <c r="AJT6">
+        <v>14.98</v>
+      </c>
+      <c r="AJU6">
+        <v>11.52</v>
+      </c>
+      <c r="AJV6">
+        <v>17.41</v>
+      </c>
+      <c r="AJW6">
+        <v>26.86</v>
+      </c>
+      <c r="AJX6">
+        <v>9.77</v>
+      </c>
+      <c r="AJY6">
+        <v>15.26</v>
+      </c>
+      <c r="AJZ6">
+        <v>25.48</v>
+      </c>
+      <c r="AKA6">
+        <v>12.44</v>
+      </c>
+      <c r="AKB6">
+        <v>14.3</v>
+      </c>
+      <c r="AKC6">
+        <v>15.09</v>
+      </c>
+      <c r="AKD6">
+        <v>7.95</v>
+      </c>
+      <c r="AKE6">
+        <v>19.010000000000002</v>
+      </c>
+      <c r="AKF6">
+        <v>16.91</v>
+      </c>
+      <c r="AKG6">
+        <v>21.8</v>
+      </c>
+      <c r="AKH6">
+        <v>9.92</v>
+      </c>
+      <c r="AKI6">
+        <v>18.170000000000002</v>
+      </c>
+      <c r="AKJ6">
+        <v>11.28</v>
+      </c>
+      <c r="AKK6">
+        <v>22.58</v>
+      </c>
+      <c r="AKL6">
+        <v>17.14</v>
+      </c>
+      <c r="AKM6">
+        <v>16.84</v>
+      </c>
+      <c r="AKN6">
+        <v>8.33</v>
+      </c>
+      <c r="AKO6">
+        <v>16.440000000000001</v>
+      </c>
+      <c r="AKP6">
+        <v>8.69</v>
+      </c>
+      <c r="AKQ6">
+        <v>17.48</v>
+      </c>
+      <c r="AKR6">
+        <v>20.6</v>
+      </c>
+      <c r="AKS6">
+        <v>15.9</v>
+      </c>
+      <c r="AKT6">
         <v>25.25</v>
       </c>
-      <c r="RW6">
-        <v>17.91</v>
-      </c>
-      <c r="RX6">
-        <v>26.4</v>
-      </c>
-      <c r="RY6">
-        <v>29.6</v>
-      </c>
-      <c r="RZ6">
-        <v>46.42</v>
-      </c>
-      <c r="SA6">
-        <v>24.66</v>
-      </c>
-      <c r="SB6">
-        <v>41.27</v>
-      </c>
-      <c r="SC6">
-        <v>21.37</v>
-      </c>
-      <c r="SD6">
-        <v>15.89</v>
-      </c>
-      <c r="SE6">
-        <v>33.04</v>
-      </c>
-      <c r="SF6">
-        <v>28.46</v>
-      </c>
-      <c r="SG6">
-        <v>29.94</v>
-      </c>
-      <c r="SH6">
-        <v>36.11</v>
-      </c>
-      <c r="SI6">
-        <v>5.5</v>
-      </c>
-      <c r="SJ6">
-        <v>27.34</v>
-      </c>
-      <c r="SK6">
-        <v>39.25</v>
-      </c>
-      <c r="SL6">
-        <v>24.54</v>
-      </c>
-      <c r="SM6">
-        <v>42.47</v>
-      </c>
-      <c r="SN6">
-        <v>21.19</v>
-      </c>
-      <c r="SO6">
-        <v>31.97</v>
-      </c>
-      <c r="SP6">
-        <v>24.39</v>
-      </c>
-      <c r="SQ6">
-        <v>5.93</v>
-      </c>
-      <c r="SR6">
-        <v>21.32</v>
-      </c>
-      <c r="SS6">
-        <v>24.11</v>
-      </c>
-      <c r="ST6">
-        <v>13.42</v>
-      </c>
-      <c r="SU6">
-        <v>32.35</v>
-      </c>
-      <c r="SV6">
-        <v>21.35</v>
-      </c>
-      <c r="SW6">
-        <v>44.39</v>
-      </c>
-      <c r="SX6">
-        <v>27.07</v>
-      </c>
-      <c r="SY6">
-        <v>23.62</v>
-      </c>
-      <c r="SZ6">
-        <v>36.69</v>
-      </c>
-      <c r="TA6">
-        <v>30.4</v>
-      </c>
-      <c r="TB6">
-        <v>38.229999999999997</v>
-      </c>
-      <c r="TC6">
-        <v>28.51</v>
-      </c>
-      <c r="TD6">
-        <v>25.75</v>
-      </c>
-      <c r="TE6">
-        <v>23.5</v>
-      </c>
-      <c r="TF6">
-        <v>20.12</v>
-      </c>
-      <c r="TG6">
-        <v>21.49</v>
-      </c>
-      <c r="TH6">
-        <v>26</v>
-      </c>
-      <c r="TI6">
-        <v>23.83</v>
-      </c>
-      <c r="TJ6">
-        <v>21.7</v>
-      </c>
-      <c r="TK6">
-        <v>30.09</v>
-      </c>
-      <c r="TL6">
-        <v>26.92</v>
-      </c>
-      <c r="TM6">
-        <v>27.49</v>
-      </c>
-      <c r="TN6">
-        <v>25.44</v>
-      </c>
-      <c r="TO6">
-        <v>30.07</v>
-      </c>
-      <c r="TP6">
-        <v>29.76</v>
-      </c>
-      <c r="TQ6">
-        <v>30</v>
-      </c>
-      <c r="TR6">
-        <v>41.48</v>
-      </c>
-      <c r="TS6">
-        <v>24.52</v>
-      </c>
-      <c r="TT6">
-        <v>17.71</v>
-      </c>
-      <c r="TU6">
-        <v>17.79</v>
-      </c>
-      <c r="TV6">
-        <v>20.99</v>
-      </c>
-      <c r="TW6">
-        <v>28.31</v>
-      </c>
-      <c r="TX6">
-        <v>25.89</v>
-      </c>
-      <c r="TY6">
-        <v>28.31</v>
-      </c>
-      <c r="TZ6">
-        <v>30.05</v>
-      </c>
-      <c r="UA6">
-        <v>30.34</v>
-      </c>
-      <c r="UB6">
-        <v>9.48</v>
-      </c>
-      <c r="UC6">
-        <v>29.64</v>
-      </c>
-      <c r="UD6">
-        <v>23.64</v>
-      </c>
-      <c r="UE6">
-        <v>24.56</v>
-      </c>
-      <c r="UF6">
-        <v>25.56</v>
-      </c>
-      <c r="UG6">
-        <v>22.04</v>
-      </c>
-      <c r="UH6">
-        <v>36.24</v>
-      </c>
-      <c r="UI6">
-        <v>23.45</v>
-      </c>
-      <c r="UJ6">
-        <v>23.51</v>
-      </c>
-      <c r="UK6">
-        <v>32.75</v>
-      </c>
-      <c r="UL6">
-        <v>34.6</v>
-      </c>
-      <c r="UM6">
-        <v>22.42</v>
-      </c>
-      <c r="UN6">
-        <v>27.48</v>
-      </c>
-      <c r="UO6">
-        <v>33.26</v>
-      </c>
-      <c r="UP6">
-        <v>25.44</v>
-      </c>
-      <c r="UQ6">
-        <v>28.9</v>
-      </c>
-      <c r="UR6">
-        <v>17.38</v>
-      </c>
-      <c r="US6">
-        <v>44.64</v>
-      </c>
-      <c r="UT6">
-        <v>25.16</v>
-      </c>
-      <c r="UU6">
-        <v>19.46</v>
-      </c>
-      <c r="UV6">
-        <v>13.6</v>
-      </c>
-      <c r="UW6">
-        <v>23.9</v>
-      </c>
-      <c r="UX6">
-        <v>25.06</v>
-      </c>
-      <c r="UY6">
-        <v>43.75</v>
-      </c>
-      <c r="UZ6">
-        <v>19.82</v>
-      </c>
-      <c r="VA6">
-        <v>11.23</v>
-      </c>
-      <c r="VB6">
-        <v>33.35</v>
-      </c>
-      <c r="VC6">
-        <v>25.7</v>
-      </c>
-      <c r="VD6">
-        <v>26.49</v>
-      </c>
-      <c r="VE6">
-        <v>28.02</v>
-      </c>
-      <c r="VF6">
-        <v>31.69</v>
-      </c>
-      <c r="VG6">
-        <v>16.350000000000001</v>
-      </c>
-      <c r="VH6">
-        <v>28.15</v>
-      </c>
-      <c r="VI6">
-        <v>22.4</v>
-      </c>
-      <c r="VJ6">
-        <v>26.09</v>
-      </c>
-      <c r="VK6">
-        <v>41.16</v>
-      </c>
-      <c r="VL6">
-        <v>24.03</v>
-      </c>
-      <c r="VM6">
-        <v>17.809999999999999</v>
-      </c>
-      <c r="VN6">
-        <v>23.22</v>
-      </c>
-      <c r="VO6">
-        <v>19.43</v>
-      </c>
-      <c r="VP6">
-        <v>31.97</v>
-      </c>
-      <c r="VQ6">
-        <v>21.98</v>
-      </c>
-      <c r="VR6">
-        <v>23.86</v>
-      </c>
-      <c r="VS6">
-        <v>32.78</v>
-      </c>
-      <c r="VT6">
-        <v>36.61</v>
-      </c>
-      <c r="VU6">
-        <v>32.24</v>
-      </c>
-      <c r="VV6">
-        <v>33.71</v>
-      </c>
-      <c r="VW6">
-        <v>35.590000000000003</v>
-      </c>
-      <c r="VX6">
-        <v>33.15</v>
-      </c>
-      <c r="VY6">
-        <v>16.809999999999999</v>
-      </c>
-      <c r="VZ6">
-        <v>27.69</v>
-      </c>
-      <c r="WA6">
-        <v>33.94</v>
-      </c>
-      <c r="WB6">
-        <v>30.61</v>
-      </c>
-      <c r="WC6">
-        <v>38.119999999999997</v>
-      </c>
-      <c r="WD6">
-        <v>23.91</v>
-      </c>
-      <c r="WE6">
-        <v>34.81</v>
-      </c>
-      <c r="WF6">
-        <v>38.04</v>
-      </c>
-      <c r="WG6">
-        <v>31.31</v>
-      </c>
-      <c r="WH6">
-        <v>37.11</v>
-      </c>
-      <c r="WI6">
-        <v>32.44</v>
-      </c>
-      <c r="WJ6">
-        <v>29.75</v>
-      </c>
-      <c r="WK6">
-        <v>20.54</v>
-      </c>
-      <c r="WL6">
-        <v>37.07</v>
-      </c>
-      <c r="WM6">
-        <v>27.28</v>
-      </c>
-      <c r="WN6">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="WO6">
-        <v>38.659999999999997</v>
-      </c>
-      <c r="WP6">
-        <v>17.37</v>
-      </c>
-      <c r="WQ6">
-        <v>29.13</v>
-      </c>
-      <c r="WR6">
-        <v>11</v>
-      </c>
-      <c r="WS6">
-        <v>29.49</v>
-      </c>
-      <c r="WT6">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="WU6">
-        <v>36.619999999999997</v>
-      </c>
-      <c r="WV6">
-        <v>35.83</v>
-      </c>
-      <c r="WW6">
-        <v>38.409999999999997</v>
-      </c>
-      <c r="WX6">
-        <v>39.729999999999997</v>
-      </c>
-      <c r="WY6">
-        <v>31.23</v>
-      </c>
-      <c r="WZ6">
-        <v>29.97</v>
-      </c>
-      <c r="XA6">
-        <v>32.92</v>
-      </c>
-      <c r="XB6">
-        <v>45.05</v>
-      </c>
-      <c r="XC6">
-        <v>24.57</v>
-      </c>
-      <c r="XD6">
-        <v>79.08</v>
-      </c>
-      <c r="XE6">
-        <v>38.6</v>
-      </c>
-      <c r="XF6">
-        <v>27.22</v>
-      </c>
-      <c r="XG6">
-        <v>38.549999999999997</v>
-      </c>
-      <c r="XH6">
-        <v>24.6</v>
-      </c>
-      <c r="XI6">
-        <v>29.26</v>
-      </c>
-      <c r="XJ6">
-        <v>61.67</v>
-      </c>
-      <c r="XK6">
-        <v>27.44</v>
-      </c>
-      <c r="XL6">
-        <v>26.44</v>
-      </c>
-      <c r="XM6">
-        <v>15.19</v>
-      </c>
-      <c r="XN6">
-        <v>5.17</v>
-      </c>
-      <c r="XO6">
-        <v>7.57</v>
-      </c>
-      <c r="XP6">
-        <v>26.78</v>
-      </c>
-      <c r="XQ6">
-        <v>34.409999999999997</v>
-      </c>
-      <c r="XR6">
-        <v>31.42</v>
-      </c>
-      <c r="XS6">
-        <v>19.809999999999999</v>
-      </c>
-      <c r="XT6">
-        <v>36.130000000000003</v>
-      </c>
-      <c r="XU6">
-        <v>27.93</v>
-      </c>
-      <c r="XV6">
-        <v>16.670000000000002</v>
-      </c>
-      <c r="XW6">
-        <v>28.81</v>
-      </c>
-      <c r="XX6">
-        <v>17.16</v>
-      </c>
-      <c r="XY6">
-        <v>36.29</v>
-      </c>
-      <c r="XZ6">
-        <v>23.29</v>
-      </c>
-      <c r="YA6">
-        <v>31.8</v>
-      </c>
-      <c r="YB6">
-        <v>25.83</v>
-      </c>
-      <c r="YC6">
-        <v>40.69</v>
-      </c>
-      <c r="YD6">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="YE6">
-        <v>25.83</v>
-      </c>
-      <c r="YF6">
-        <v>41.83</v>
-      </c>
-      <c r="YG6">
-        <v>36.04</v>
-      </c>
-      <c r="YH6">
-        <v>34.04</v>
-      </c>
-      <c r="YI6">
-        <v>39.369999999999997</v>
-      </c>
-      <c r="YJ6">
-        <v>32.21</v>
-      </c>
-      <c r="YK6">
-        <v>41.22</v>
-      </c>
-      <c r="YL6">
-        <v>20.54</v>
-      </c>
-      <c r="YM6">
-        <v>16.25</v>
-      </c>
-      <c r="YN6">
-        <v>28.86</v>
-      </c>
-      <c r="YO6">
-        <v>36.090000000000003</v>
-      </c>
-      <c r="YP6">
-        <v>31.59</v>
-      </c>
-      <c r="YQ6">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="YR6">
-        <v>11.93</v>
-      </c>
-      <c r="YS6">
-        <v>7.81</v>
-      </c>
-      <c r="YT6">
-        <v>43.35</v>
-      </c>
-      <c r="YU6">
-        <v>31.93</v>
-      </c>
-      <c r="YV6">
-        <v>37.97</v>
-      </c>
-      <c r="YW6">
-        <v>32.83</v>
-      </c>
-      <c r="YX6">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="YY6">
-        <v>37.590000000000003</v>
-      </c>
-      <c r="YZ6">
-        <v>22.29</v>
-      </c>
-      <c r="ZA6">
-        <v>33.01</v>
-      </c>
-      <c r="ZB6">
-        <v>47.47</v>
-      </c>
-      <c r="ZC6">
-        <v>26.76</v>
-      </c>
-      <c r="ZD6">
-        <v>45.82</v>
-      </c>
-      <c r="ZE6">
-        <v>31.29</v>
-      </c>
-      <c r="ZF6">
-        <v>31.89</v>
-      </c>
-      <c r="ZG6">
-        <v>34.06</v>
-      </c>
-      <c r="ZH6">
-        <v>44.13</v>
-      </c>
-      <c r="ZI6">
-        <v>39.869999999999997</v>
-      </c>
-      <c r="ZJ6">
-        <v>23.85</v>
-      </c>
-      <c r="ZK6">
-        <v>30.41</v>
-      </c>
-      <c r="ZL6">
-        <v>10.050000000000001</v>
-      </c>
-      <c r="ZM6">
-        <v>24.07</v>
-      </c>
-      <c r="ZN6">
-        <v>23.53</v>
-      </c>
-      <c r="ZO6">
-        <v>31.38</v>
-      </c>
-      <c r="ZP6">
-        <v>22.32</v>
-      </c>
-      <c r="ZQ6">
-        <v>31.25</v>
-      </c>
-      <c r="ZR6">
-        <v>27.66</v>
-      </c>
-      <c r="ZS6">
-        <v>9.35</v>
-      </c>
-      <c r="ZT6">
-        <v>33.43</v>
-      </c>
-      <c r="ZU6">
-        <v>34.33</v>
-      </c>
-      <c r="ZV6">
-        <v>34.25</v>
-      </c>
-      <c r="ZW6">
-        <v>34.33</v>
-      </c>
-      <c r="ZX6">
-        <v>26.67</v>
-      </c>
-      <c r="ZY6">
-        <v>23.15</v>
-      </c>
-      <c r="ZZ6">
-        <v>19.690000000000001</v>
-      </c>
-      <c r="AAA6">
-        <v>34.369999999999997</v>
-      </c>
-      <c r="AAB6">
-        <v>28.42</v>
-      </c>
-      <c r="AAC6">
-        <v>27.44</v>
-      </c>
-      <c r="AAD6">
-        <v>28.83</v>
-      </c>
-      <c r="AAE6">
-        <v>26.67</v>
-      </c>
-      <c r="AAF6">
-        <v>20.25</v>
-      </c>
-      <c r="AAG6">
-        <v>26.37</v>
-      </c>
-      <c r="AAH6">
-        <v>22.69</v>
-      </c>
-      <c r="AAI6">
-        <v>32.64</v>
-      </c>
-      <c r="AAJ6">
-        <v>53.58</v>
-      </c>
-      <c r="AAK6">
-        <v>41.57</v>
-      </c>
-      <c r="AAL6">
-        <v>24.48</v>
-      </c>
-      <c r="AAM6">
-        <v>40.049999999999997</v>
-      </c>
-      <c r="AAN6">
-        <v>36.99</v>
-      </c>
-      <c r="AAO6">
-        <v>33.47</v>
-      </c>
-      <c r="AAP6">
-        <v>38.14</v>
-      </c>
-      <c r="AAQ6">
-        <v>38.619999999999997</v>
-      </c>
-      <c r="AAR6">
-        <v>38.85</v>
-      </c>
-      <c r="AAS6">
-        <v>10.16</v>
-      </c>
-      <c r="AAT6">
-        <v>32.299999999999997</v>
-      </c>
-      <c r="AAU6">
-        <v>25.38</v>
-      </c>
-      <c r="AAV6">
-        <v>35.130000000000003</v>
-      </c>
-      <c r="AAW6">
-        <v>31.69</v>
-      </c>
-      <c r="AAX6">
-        <v>10.61</v>
-      </c>
-      <c r="AAY6">
-        <v>29.8</v>
-      </c>
-      <c r="AAZ6">
-        <v>29.74</v>
-      </c>
-      <c r="ABA6">
-        <v>36.549999999999997</v>
-      </c>
-      <c r="ABB6">
-        <v>44.04</v>
-      </c>
-      <c r="ABC6">
-        <v>31.57</v>
-      </c>
-      <c r="ABD6">
-        <v>25.68</v>
-      </c>
-      <c r="ABE6">
-        <v>34.43</v>
-      </c>
-      <c r="ABF6">
-        <v>51.38</v>
-      </c>
-      <c r="ABG6">
-        <v>28.09</v>
-      </c>
-      <c r="ABH6">
-        <v>32.4</v>
-      </c>
-      <c r="ABI6">
-        <v>34.729999999999997</v>
-      </c>
-      <c r="ABJ6">
-        <v>19.149999999999999</v>
-      </c>
-      <c r="ABK6">
-        <v>29.38</v>
-      </c>
-      <c r="ABL6">
-        <v>37.64</v>
-      </c>
-      <c r="ABM6">
-        <v>26.55</v>
-      </c>
-      <c r="ABN6">
-        <v>39.700000000000003</v>
-      </c>
-      <c r="ABO6">
-        <v>29.74</v>
-      </c>
-      <c r="ABP6">
-        <v>38.47</v>
-      </c>
-      <c r="ABQ6">
-        <v>40.17</v>
-      </c>
-      <c r="ABR6">
-        <v>29.49</v>
-      </c>
-      <c r="ABS6">
-        <v>41.71</v>
-      </c>
-      <c r="ABT6">
-        <v>30.05</v>
-      </c>
-      <c r="ABU6">
-        <v>25.05</v>
-      </c>
-      <c r="ABV6">
-        <v>41.15</v>
-      </c>
-      <c r="ABW6">
-        <v>31.56</v>
-      </c>
-      <c r="ABX6">
-        <v>29.87</v>
-      </c>
-      <c r="ABY6">
-        <v>30.87</v>
-      </c>
-      <c r="ABZ6">
-        <v>41.89</v>
-      </c>
-      <c r="ACA6">
-        <v>20.62</v>
-      </c>
-      <c r="ACB6">
-        <v>34.659999999999997</v>
-      </c>
-      <c r="ACC6">
-        <v>27.61</v>
-      </c>
-      <c r="ACD6">
-        <v>32.520000000000003</v>
-      </c>
-      <c r="ACE6">
-        <v>22.75</v>
-      </c>
-      <c r="ACF6">
-        <v>27.1</v>
-      </c>
-      <c r="ACG6">
-        <v>21.4</v>
-      </c>
-      <c r="ACH6">
-        <v>33.049999999999997</v>
-      </c>
-      <c r="ACI6">
-        <v>29.15</v>
-      </c>
-      <c r="ACJ6">
-        <v>6.33</v>
-      </c>
-      <c r="ACK6">
-        <v>29.39</v>
-      </c>
-      <c r="ACL6">
-        <v>28.23</v>
-      </c>
-      <c r="ACM6">
-        <v>36.03</v>
-      </c>
-      <c r="ACN6">
-        <v>29.61</v>
-      </c>
-      <c r="ACO6">
-        <v>22.7</v>
-      </c>
-      <c r="ACP6">
-        <v>44.57</v>
-      </c>
-      <c r="ACQ6">
-        <v>37.96</v>
-      </c>
-      <c r="ACR6">
-        <v>37.83</v>
-      </c>
-      <c r="ACS6">
-        <v>35.97</v>
-      </c>
-      <c r="ACT6">
-        <v>36.5</v>
-      </c>
-      <c r="ACU6">
-        <v>35.909999999999997</v>
-      </c>
-      <c r="ACV6">
-        <v>42.32</v>
-      </c>
-      <c r="ACW6">
-        <v>32.630000000000003</v>
-      </c>
-      <c r="ACX6">
-        <v>23.04</v>
-      </c>
-      <c r="ACY6">
-        <v>30.88</v>
-      </c>
-      <c r="ACZ6">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="ADA6">
-        <v>28.45</v>
-      </c>
-      <c r="ADB6">
-        <v>16.190000000000001</v>
-      </c>
-      <c r="ADC6">
-        <v>39.840000000000003</v>
-      </c>
-      <c r="ADD6">
-        <v>45.14</v>
-      </c>
-      <c r="ADE6">
-        <v>32.049999999999997</v>
-      </c>
-      <c r="ADF6">
-        <v>23.27</v>
-      </c>
-      <c r="ADG6">
-        <v>38.090000000000003</v>
-      </c>
-      <c r="ADH6">
-        <v>35.31</v>
-      </c>
-      <c r="ADI6">
-        <v>44.81</v>
-      </c>
-      <c r="ADJ6">
-        <v>36.24</v>
-      </c>
-      <c r="ADK6">
-        <v>39.43</v>
-      </c>
-      <c r="ADL6">
-        <v>21.76</v>
-      </c>
-      <c r="ADM6">
-        <v>21.82</v>
-      </c>
-      <c r="ADN6">
-        <v>26.67</v>
-      </c>
-      <c r="ADO6">
-        <v>30.86</v>
-      </c>
-      <c r="ADP6">
-        <v>30.87</v>
-      </c>
-      <c r="ADQ6">
-        <v>31.67</v>
-      </c>
-      <c r="ADR6">
-        <v>28.73</v>
-      </c>
-      <c r="ADS6">
-        <v>23.91</v>
-      </c>
-      <c r="ADT6">
-        <v>39.93</v>
-      </c>
-      <c r="ADU6">
-        <v>25.87</v>
-      </c>
-      <c r="ADV6">
-        <v>42.91</v>
-      </c>
-      <c r="ADW6">
-        <v>24.98</v>
-      </c>
-      <c r="ADX6">
-        <v>26.49</v>
-      </c>
-      <c r="ADY6">
-        <v>48.84</v>
-      </c>
-      <c r="ADZ6">
-        <v>29.8</v>
-      </c>
-      <c r="AEA6">
-        <v>24.15</v>
-      </c>
-      <c r="AEB6">
-        <v>31.5</v>
-      </c>
-      <c r="AEC6">
-        <v>40.72</v>
-      </c>
-      <c r="AED6">
-        <v>30.25</v>
-      </c>
-      <c r="AEE6">
-        <v>40.61</v>
-      </c>
-      <c r="AEF6">
-        <v>34.74</v>
-      </c>
-      <c r="AEG6">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="AEH6">
-        <v>26.85</v>
-      </c>
-      <c r="AEI6">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="AEJ6">
-        <v>29.29</v>
-      </c>
-      <c r="AEK6">
-        <v>29.85</v>
-      </c>
-      <c r="AEL6">
-        <v>33.450000000000003</v>
-      </c>
-      <c r="AEM6">
-        <v>31.26</v>
-      </c>
-      <c r="AEN6">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="AEO6">
-        <v>35</v>
-      </c>
-      <c r="AEP6">
-        <v>32.6</v>
-      </c>
-      <c r="AEQ6">
-        <v>29.24</v>
-      </c>
-      <c r="AER6">
-        <v>26.95</v>
-      </c>
-      <c r="AES6">
-        <v>16.66</v>
-      </c>
-      <c r="AET6">
-        <v>32.47</v>
-      </c>
-      <c r="AEU6">
-        <v>32.57</v>
-      </c>
-      <c r="AEV6">
-        <v>28.17</v>
-      </c>
-      <c r="AEW6">
-        <v>36.32</v>
-      </c>
-      <c r="AEX6">
-        <v>24.31</v>
-      </c>
-      <c r="AEY6">
-        <v>34.32</v>
-      </c>
-      <c r="AEZ6">
-        <v>41.53</v>
-      </c>
-      <c r="AFA6">
-        <v>28.21</v>
-      </c>
-      <c r="AFB6">
-        <v>25.2</v>
-      </c>
-      <c r="AFC6">
-        <v>33.840000000000003</v>
-      </c>
-      <c r="AFD6">
-        <v>36.58</v>
-      </c>
-      <c r="AFE6">
-        <v>23.08</v>
-      </c>
-      <c r="AFF6">
-        <v>31.76</v>
-      </c>
-      <c r="AFG6">
-        <v>33.909999999999997</v>
-      </c>
-      <c r="AFH6">
-        <v>30.57</v>
-      </c>
-      <c r="AFI6">
-        <v>26.91</v>
-      </c>
-      <c r="AFJ6">
-        <v>24.54</v>
-      </c>
-      <c r="AFK6">
-        <v>28.6</v>
-      </c>
-      <c r="AFL6">
-        <v>24.58</v>
-      </c>
-      <c r="AFM6">
-        <v>25.52</v>
-      </c>
-      <c r="AFN6">
-        <v>24.94</v>
-      </c>
-      <c r="AFO6">
-        <v>20.38</v>
-      </c>
-      <c r="AFP6">
-        <v>25.19</v>
-      </c>
-      <c r="AFQ6">
-        <v>18.68</v>
-      </c>
-      <c r="AFR6">
-        <v>31.78</v>
-      </c>
-      <c r="AFS6">
-        <v>31.5</v>
-      </c>
-      <c r="AFT6">
-        <v>33.24</v>
-      </c>
-      <c r="AFU6">
-        <v>37.11</v>
-      </c>
-      <c r="AFV6">
-        <v>35.630000000000003</v>
-      </c>
-      <c r="AFW6">
-        <v>21.12</v>
-      </c>
-      <c r="AFX6">
-        <v>24.9</v>
-      </c>
-      <c r="AFY6">
-        <v>31.66</v>
-      </c>
-      <c r="AFZ6">
-        <v>20.39</v>
-      </c>
-      <c r="AGA6">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="AGB6">
-        <v>23.71</v>
-      </c>
-      <c r="AGC6">
-        <v>23.84</v>
-      </c>
-      <c r="AGD6">
-        <v>25.81</v>
-      </c>
-      <c r="AGE6">
-        <v>29.28</v>
-      </c>
-      <c r="AGF6">
-        <v>5.55</v>
-      </c>
-      <c r="AGG6">
-        <v>32.01</v>
-      </c>
-      <c r="AGH6">
-        <v>35.28</v>
-      </c>
-      <c r="AGI6">
-        <v>25.49</v>
-      </c>
-      <c r="AGJ6">
-        <v>20.18</v>
-      </c>
-      <c r="AGK6">
-        <v>22.31</v>
-      </c>
-      <c r="AGL6">
-        <v>27.52</v>
-      </c>
-      <c r="AGM6">
-        <v>4.84</v>
-      </c>
-      <c r="AGN6">
-        <v>36.1</v>
-      </c>
-      <c r="AGO6">
-        <v>27.8</v>
-      </c>
-      <c r="AGP6">
-        <v>30.86</v>
-      </c>
-      <c r="AGQ6">
-        <v>36.86</v>
-      </c>
-      <c r="AGR6">
-        <v>36.909999999999997</v>
-      </c>
-      <c r="AGS6">
-        <v>24.46</v>
-      </c>
-      <c r="AGT6">
-        <v>29.2</v>
-      </c>
-      <c r="AGU6">
-        <v>13.99</v>
-      </c>
-      <c r="AGV6">
-        <v>38.31</v>
-      </c>
-      <c r="AGW6">
-        <v>32.5</v>
-      </c>
-      <c r="AGX6">
-        <v>47.04</v>
-      </c>
-      <c r="AGY6">
-        <v>33.81</v>
-      </c>
-      <c r="AGZ6">
-        <v>46.57</v>
-      </c>
-      <c r="AHA6">
-        <v>34.71</v>
-      </c>
-      <c r="AHB6">
-        <v>28.36</v>
-      </c>
-      <c r="AHC6">
-        <v>36.89</v>
-      </c>
-      <c r="AHD6">
-        <v>28.94</v>
-      </c>
-      <c r="AHE6">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="AHF6">
-        <v>29.89</v>
-      </c>
-      <c r="AHG6">
-        <v>29.83</v>
-      </c>
-      <c r="AHH6">
-        <v>35.049999999999997</v>
-      </c>
-      <c r="AHI6">
-        <v>27.23</v>
-      </c>
-      <c r="AHJ6">
-        <v>36.75</v>
-      </c>
-      <c r="AHK6">
-        <v>39.54</v>
-      </c>
-      <c r="AHL6">
-        <v>40.24</v>
-      </c>
-      <c r="AHM6">
-        <v>26.28</v>
-      </c>
-      <c r="AHN6">
-        <v>41.38</v>
-      </c>
-      <c r="AHO6">
-        <v>26.67</v>
-      </c>
-      <c r="AHP6">
-        <v>37.479999999999997</v>
-      </c>
-      <c r="AHQ6">
-        <v>31.72</v>
-      </c>
-      <c r="AHR6">
-        <v>28.69</v>
-      </c>
-      <c r="AHS6">
-        <v>11.51</v>
-      </c>
-      <c r="AHT6">
-        <v>24.47</v>
-      </c>
-      <c r="AHU6">
-        <v>28.47</v>
-      </c>
-      <c r="AHV6">
-        <v>20.78</v>
-      </c>
-      <c r="AHW6">
-        <v>26.25</v>
-      </c>
-      <c r="AHX6">
-        <v>35.950000000000003</v>
-      </c>
-      <c r="AHY6">
-        <v>29.76</v>
-      </c>
-      <c r="AHZ6">
-        <v>16.12</v>
-      </c>
-      <c r="AIA6">
-        <v>28.21</v>
-      </c>
-      <c r="AIB6">
-        <v>32.68</v>
-      </c>
-      <c r="AIC6">
-        <v>22.26</v>
-      </c>
-      <c r="AID6">
-        <v>40.54</v>
-      </c>
-      <c r="AIE6">
-        <v>36.369999999999997</v>
-      </c>
-      <c r="AIF6">
-        <v>19.690000000000001</v>
-      </c>
-      <c r="AIG6">
-        <v>34.880000000000003</v>
-      </c>
-      <c r="AIH6">
-        <v>33.590000000000003</v>
-      </c>
-      <c r="AII6">
-        <v>26.55</v>
-      </c>
-      <c r="AIJ6">
-        <v>24.32</v>
-      </c>
-      <c r="AIK6">
-        <v>36.630000000000003</v>
-      </c>
-      <c r="AIL6">
-        <v>28.94</v>
-      </c>
-      <c r="AIM6">
-        <v>27.77</v>
-      </c>
-      <c r="AIN6">
-        <v>28.94</v>
-      </c>
-      <c r="AIO6">
-        <v>31.22</v>
-      </c>
-      <c r="AIP6">
-        <v>8.89</v>
-      </c>
-      <c r="AIQ6">
-        <v>22.58</v>
-      </c>
-      <c r="AIR6">
-        <v>37.979999999999997</v>
-      </c>
-      <c r="AIS6">
-        <v>8.8699999999999992</v>
-      </c>
-      <c r="AIT6">
-        <v>23.31</v>
-      </c>
-      <c r="AIU6">
-        <v>29.92</v>
-      </c>
-      <c r="AIV6">
-        <v>39.479999999999997</v>
-      </c>
-      <c r="AIW6">
-        <v>54.93</v>
-      </c>
-      <c r="AIX6">
-        <v>31.17</v>
-      </c>
-      <c r="AIY6">
-        <v>36.07</v>
-      </c>
-      <c r="AIZ6">
-        <v>29.36</v>
-      </c>
-      <c r="AJA6">
-        <v>43.34</v>
-      </c>
-      <c r="AJB6">
-        <v>27.8</v>
-      </c>
-      <c r="AJC6">
-        <v>31.64</v>
-      </c>
-      <c r="AJD6">
-        <v>30.48</v>
-      </c>
-      <c r="AJE6">
-        <v>28.29</v>
-      </c>
-      <c r="AJF6">
-        <v>33.479999999999997</v>
-      </c>
-      <c r="AJG6">
-        <v>28.77</v>
-      </c>
-      <c r="AJH6">
-        <v>31.07</v>
-      </c>
-      <c r="AJI6">
-        <v>24.88</v>
-      </c>
-      <c r="AJJ6">
-        <v>40.9</v>
-      </c>
-      <c r="AJK6">
-        <v>34.14</v>
-      </c>
-      <c r="AJL6">
-        <v>31.93</v>
-      </c>
-      <c r="AJM6">
-        <v>5.37</v>
-      </c>
-      <c r="AJN6">
-        <v>30.95</v>
-      </c>
-      <c r="AJO6">
-        <v>27.5</v>
-      </c>
-      <c r="AJP6">
-        <v>26.61</v>
-      </c>
-      <c r="AJQ6">
-        <v>32.49</v>
-      </c>
-      <c r="AJR6">
-        <v>29.24</v>
-      </c>
-      <c r="AJS6">
-        <v>34.22</v>
-      </c>
-      <c r="AJT6">
-        <v>29.37</v>
-      </c>
-      <c r="AJU6">
-        <v>27.18</v>
-      </c>
-      <c r="AJV6">
-        <v>24.95</v>
-      </c>
-      <c r="AJW6">
-        <v>43.81</v>
-      </c>
-      <c r="AJX6">
-        <v>40.520000000000003</v>
-      </c>
-      <c r="AJY6">
-        <v>31.99</v>
-      </c>
-      <c r="AJZ6">
-        <v>37.369999999999997</v>
-      </c>
-      <c r="AKA6">
-        <v>26.08</v>
-      </c>
-      <c r="AKB6">
-        <v>8.93</v>
-      </c>
-      <c r="AKC6">
-        <v>23.23</v>
-      </c>
-      <c r="AKD6">
-        <v>20.85</v>
-      </c>
-      <c r="AKE6">
-        <v>24</v>
-      </c>
-      <c r="AKF6">
-        <v>31.51</v>
-      </c>
-      <c r="AKG6">
-        <v>30.19</v>
-      </c>
-      <c r="AKH6">
-        <v>26.47</v>
-      </c>
-      <c r="AKI6">
-        <v>26.29</v>
-      </c>
-      <c r="AKJ6">
-        <v>25.61</v>
-      </c>
-      <c r="AKK6">
-        <v>30.23</v>
-      </c>
-      <c r="AKL6">
-        <v>26.52</v>
-      </c>
-      <c r="AKM6">
-        <v>32.65</v>
-      </c>
-      <c r="AKN6">
-        <v>6.06</v>
-      </c>
-      <c r="AKO6">
-        <v>25.88</v>
-      </c>
-      <c r="AKP6">
-        <v>26.33</v>
-      </c>
-      <c r="AKQ6">
-        <v>38.22</v>
-      </c>
-      <c r="AKR6">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="AKS6">
-        <v>44.07</v>
-      </c>
-      <c r="AKT6">
-        <v>39.68</v>
-      </c>
       <c r="AKU6">
-        <v>27.19</v>
+        <v>14.76</v>
       </c>
       <c r="AKV6">
-        <v>25.86</v>
+        <v>14.93</v>
       </c>
       <c r="AKW6">
-        <v>29.71</v>
+        <v>13.93</v>
       </c>
       <c r="AKX6">
-        <v>27.08</v>
+        <v>16.28</v>
       </c>
       <c r="AKY6">
-        <v>36.880000000000003</v>
+        <v>15.76</v>
       </c>
       <c r="AKZ6">
-        <v>28.48</v>
+        <v>15.63</v>
       </c>
       <c r="ALA6">
-        <v>11.34</v>
+        <v>15.68</v>
       </c>
       <c r="ALB6">
-        <v>7.11</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="ALC6">
-        <v>31.72</v>
+        <v>13.43</v>
       </c>
       <c r="ALD6">
-        <v>13.56</v>
+        <v>18.98</v>
       </c>
       <c r="ALE6">
-        <v>22.98</v>
+        <v>11.54</v>
       </c>
       <c r="ALF6">
-        <v>28.55</v>
+        <v>13.88</v>
       </c>
       <c r="ALG6">
-        <v>28.94</v>
+        <v>16.93</v>
       </c>
       <c r="ALH6">
-        <v>32.32</v>
+        <v>7.93</v>
       </c>
       <c r="ALI6">
-        <v>24.31</v>
+        <v>9.56</v>
       </c>
       <c r="ALJ6">
-        <v>34.159999999999997</v>
+        <v>13.11</v>
       </c>
       <c r="ALK6">
-        <v>22.69</v>
+        <v>16.04</v>
       </c>
       <c r="ALL6">
-        <v>32.020000000000003</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="ALM6">
-        <v>31.85</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="ALN6">
-        <v>29.13</v>
+        <v>25.32</v>
       </c>
     </row>
-    <row r="7" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>3</v>
       </c>
       <c r="C7">
         <f>ROUND(AVERAGE(C6:ALN6),2)</f>
-        <v>27.66</v>
+        <v>15.92</v>
       </c>
     </row>
-    <row r="9" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -27555,7 +27555,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="10" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
         <v>2</v>
@@ -30561,7 +30561,7 @@
         <v>23.24</v>
       </c>
     </row>
-    <row r="11" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>3</v>
       </c>
@@ -30576,8 +30576,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A5:A6"/>
     <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A5:A6"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30587,12 +30587,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:ALN14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.59765625" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -33600,7 +33600,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="2" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" t="s">
         <v>2</v>
@@ -36606,7 +36606,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="3" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -36615,7 +36615,7 @@
         <v>14.41</v>
       </c>
     </row>
-    <row r="4" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -36623,7 +36623,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="6" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -39631,7 +39631,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="7" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" t="s">
         <v>2</v>
@@ -42637,7 +42637,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -42646,7 +42646,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="9" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -42654,7 +42654,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="11" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -45662,7 +45662,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="12" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
         <v>2</v>
@@ -48668,7 +48668,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="13" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>6</v>
       </c>
@@ -48677,7 +48677,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="14" spans="1:1002" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:1002" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>7</v>
       </c>
